--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2835" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3072" uniqueCount="376">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T11:15:06+05:30</t>
+    <t>2026-05-13T15:29:14+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,6 +559,24 @@
 purposes.</t>
   </si>
   <si>
+    <t>Attachment.extension:helperFile</t>
+  </si>
+  <si>
+    <t>helperFile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/attachment-helperFile}
+</t>
+  </si>
+  <si>
+    <t>Helper file associated with the attachment</t>
+  </si>
+  <si>
+    <t>Provides the path or filename of an auxiliary/helper file required
+for interpretation, transformation, rendering, or processing of
+the attachment content.</t>
+  </si>
+  <si>
     <t>Attachment.contentType</t>
   </si>
   <si>
@@ -715,6 +733,49 @@
     <t>This is often tracked as an integrity issue for use of the attachment.</t>
   </si>
   <si>
+    <t>attachment-helperFile</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/StructureDefinition/attachment-helperFile</t>
+  </si>
+  <si>
+    <t>AttachmentHelperFile</t>
+  </si>
+  <si>
+    <t>Attachment Helper File</t>
+  </si>
+  <si>
+    <t>Provides the path or filename of a helper/supporting file associated
+with an Attachment.
+This extension is intended for scenarios in which the consumer of
+the attachment requires an auxiliary/helper file in order to correctly
+interpret, process, transform, or render the attachment content.
+Examples include:
+- XSLT files associated with XML documents
+- Schema files
+- Rendering templates
+- Transformation scripts
+- Supporting metadata files</t>
+  </si>
+  <si>
+    <t>Supports association of auxiliary/helper files required for proper
+interpretation or processing of an attachment.</t>
+  </si>
+  <si>
+    <t>element:Attachment</t>
+  </si>
+  <si>
+    <t>Path or filename of associated helper/supporting file</t>
+  </si>
+  <si>
+    <t>Specifies the path, filename, or storage reference of a helper/supporting
+file associated with the attachment.</t>
+  </si>
+  <si>
+    <t>The interpretation and usage of the helper file is dependent upon
+the attachment content type and consuming application.</t>
+  </si>
+  <si>
     <t>attachment-inlineDataSavedAsFile</t>
   </si>
   <si>
@@ -729,9 +790,6 @@
   <si>
     <t>Supports workflows in which inline binary content is externalized
 into object storage and referenced through Attachment.url.</t>
-  </si>
-  <si>
-    <t>element:Attachment</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -1346,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B216"/>
+  <dimension ref="A1:B238"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1866,7 +1924,7 @@
         <v>2</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67">
@@ -1874,7 +1932,7 @@
         <v>4</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68">
@@ -1890,7 +1948,7 @@
         <v>8</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70">
@@ -1898,7 +1956,7 @@
         <v>10</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="71">
@@ -1952,7 +2010,7 @@
         <v>23</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>161</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78">
@@ -1960,7 +2018,7 @@
         <v>25</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="79">
@@ -2022,7 +2080,7 @@
         <v>128</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87">
@@ -2038,7 +2096,7 @@
         <v>2</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89">
@@ -2046,7 +2104,7 @@
         <v>4</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="90">
@@ -2062,7 +2120,7 @@
         <v>8</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="92">
@@ -2070,7 +2128,7 @@
         <v>10</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="93">
@@ -2124,7 +2182,7 @@
         <v>23</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100">
@@ -2132,7 +2190,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="101">
@@ -2194,7 +2252,7 @@
         <v>128</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109">
@@ -2210,7 +2268,7 @@
         <v>2</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="111">
@@ -2218,7 +2276,7 @@
         <v>4</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="112">
@@ -2234,7 +2292,7 @@
         <v>8</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="114">
@@ -2242,7 +2300,7 @@
         <v>10</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="115">
@@ -2296,14 +2354,16 @@
         <v>23</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>238</v>
+        <v>166</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B122" s="2"/>
+      <c r="B122" t="s" s="2">
+        <v>244</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
@@ -2332,7 +2392,7 @@
         <v>32</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>239</v>
+        <v>126</v>
       </c>
     </row>
     <row r="127">
@@ -2340,7 +2400,7 @@
         <v>34</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>240</v>
+        <v>127</v>
       </c>
     </row>
     <row r="128">
@@ -2360,48 +2420,48 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s" s="1">
+      <c r="A130" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B130" t="s" s="1">
+      <c r="B131" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>299</v>
+        <v>248</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>7</v>
+        <v>249</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>300</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>250</v>
@@ -2409,126 +2469,124 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>13</v>
+        <v>251</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B137" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>16</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>251</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>301</v>
+        <v>252</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>29</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>126</v>
+        <v>31</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>127</v>
+        <v>253</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>37</v>
+        <v>254</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>302</v>
+        <v>39</v>
       </c>
     </row>
     <row r="152">
@@ -2544,7 +2602,7 @@
         <v>2</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="154">
@@ -2552,7 +2610,7 @@
         <v>4</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="155">
@@ -2568,7 +2626,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="157">
@@ -2576,7 +2634,7 @@
         <v>10</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="158">
@@ -2630,7 +2688,7 @@
         <v>23</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="165">
@@ -2638,7 +2696,7 @@
         <v>25</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="166">
@@ -2700,7 +2758,7 @@
         <v>128</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="174">
@@ -2716,7 +2774,7 @@
         <v>2</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="176">
@@ -2724,7 +2782,7 @@
         <v>4</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="177">
@@ -2740,7 +2798,7 @@
         <v>8</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="179">
@@ -2748,7 +2806,7 @@
         <v>10</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>315</v>
+        <v>285</v>
       </c>
     </row>
     <row r="180">
@@ -2802,7 +2860,7 @@
         <v>23</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>316</v>
+        <v>286</v>
       </c>
     </row>
     <row r="187">
@@ -2810,7 +2868,7 @@
         <v>25</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="188">
@@ -2840,7 +2898,7 @@
         <v>32</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>318</v>
+        <v>126</v>
       </c>
     </row>
     <row r="192">
@@ -2848,7 +2906,7 @@
         <v>34</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>319</v>
+        <v>127</v>
       </c>
     </row>
     <row r="193">
@@ -2868,175 +2926,347 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="s" s="1">
+      <c r="A195" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B195" t="s" s="1">
+      <c r="B196" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>353</v>
+        <v>326</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>7</v>
+        <v>327</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>354</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>355</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>13</v>
+        <v>329</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B202" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>16</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>356</v>
+        <v>22</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>357</v>
+        <v>330</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B209" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>331</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B210" t="s" s="2">
-        <v>29</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>126</v>
+        <v>31</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>127</v>
+        <v>332</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>37</v>
+        <v>333</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B217" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B224" s="2"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B231" s="2"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="B216" t="s" s="2">
-        <v>358</v>
+      <c r="B238" t="s" s="2">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3046,7 +3276,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK73"/>
+  <dimension ref="A1:AK79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="28.51953125" customWidth="true" bestFit="true"/>
@@ -4978,9 +5208,11 @@
         <v>167</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="D19" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="E19" t="s" s="2">
         <v>22</v>
       </c>
@@ -4998,21 +5230,19 @@
         <v>22</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O19" s="2"/>
-      <c r="P19" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
         <v>22</v>
       </c>
@@ -5024,7 +5254,7 @@
         <v>22</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>172</v>
+        <v>22</v>
       </c>
       <c r="V19" t="s" s="2">
         <v>22</v>
@@ -5036,13 +5266,13 @@
         <v>22</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>173</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>174</v>
+        <v>22</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="AB19" t="s" s="2">
         <v>22</v>
@@ -5060,19 +5290,19 @@
         <v>22</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -5080,10 +5310,10 @@
         <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -5106,17 +5336,17 @@
         <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Q20" t="s" s="2">
         <v>22</v>
@@ -5129,26 +5359,26 @@
         <v>22</v>
       </c>
       <c r="U20" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AA20" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="V20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="AB20" t="s" s="2">
         <v>22</v>
       </c>
@@ -5165,7 +5395,7 @@
         <v>22</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>76</v>
@@ -5185,10 +5415,10 @@
         <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -5199,7 +5429,7 @@
         <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>22</v>
@@ -5208,22 +5438,20 @@
         <v>22</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="Q21" t="s" s="2">
         <v>22</v>
@@ -5236,7 +5464,7 @@
         <v>22</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="V21" t="s" s="2">
         <v>22</v>
@@ -5248,13 +5476,13 @@
         <v>22</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>22</v>
+        <v>188</v>
       </c>
       <c r="AB21" t="s" s="2">
         <v>22</v>
@@ -5272,7 +5500,7 @@
         <v>22</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>76</v>
@@ -5292,10 +5520,10 @@
         <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -5303,10 +5531,10 @@
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>22</v>
@@ -5315,22 +5543,22 @@
         <v>22</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="O22" t="s" s="2">
+      <c r="P22" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="Q22" t="s" s="2">
         <v>22</v>
@@ -5343,7 +5571,7 @@
         <v>22</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>196</v>
+        <v>22</v>
       </c>
       <c r="V22" t="s" s="2">
         <v>22</v>
@@ -5379,7 +5607,7 @@
         <v>22</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>76</v>
@@ -5399,10 +5627,10 @@
         <v>143</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -5410,7 +5638,7 @@
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>85</v>
@@ -5425,19 +5653,19 @@
         <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="P23" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="P23" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="Q23" t="s" s="2">
         <v>22</v>
@@ -5450,7 +5678,7 @@
         <v>22</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="V23" t="s" s="2">
         <v>22</v>
@@ -5486,7 +5714,7 @@
         <v>22</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>76</v>
@@ -5506,10 +5734,10 @@
         <v>143</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -5532,7 +5760,7 @@
         <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>204</v>
@@ -5593,7 +5821,7 @@
         <v>22</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>76</v>
@@ -5639,7 +5867,7 @@
         <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>209</v>
@@ -5647,9 +5875,11 @@
       <c r="N25" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="O25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q25" t="s" s="2">
         <v>22</v>
@@ -5662,7 +5892,7 @@
         <v>22</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="V25" t="s" s="2">
         <v>22</v>
@@ -5744,7 +5974,7 @@
         <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>214</v>
@@ -5767,7 +5997,7 @@
         <v>22</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>22</v>
+        <v>217</v>
       </c>
       <c r="V26" t="s" s="2">
         <v>22</v>
@@ -5820,13 +6050,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>217</v>
+        <v>143</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -5837,7 +6067,7 @@
         <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>22</v>
@@ -5846,19 +6076,21 @@
         <v>22</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="M27" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="Q27" t="s" s="2">
         <v>22</v>
       </c>
@@ -5906,30 +6138,30 @@
         <v>22</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -5940,7 +6172,7 @@
         <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>22</v>
@@ -5952,13 +6184,13 @@
         <v>22</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>87</v>
+        <v>225</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>88</v>
+        <v>226</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -6009,30 +6241,30 @@
         <v>22</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -6043,7 +6275,7 @@
         <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>22</v>
@@ -6055,13 +6287,13 @@
         <v>22</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -6100,42 +6332,42 @@
         <v>22</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -6143,10 +6375,10 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>22</v>
@@ -6158,24 +6390,22 @@
         <v>22</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R30" s="2"/>
       <c r="S30" t="s" s="2">
-        <v>218</v>
+        <v>22</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>22</v>
@@ -6205,42 +6435,42 @@
         <v>22</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -6263,22 +6493,24 @@
         <v>22</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>223</v>
+        <v>134</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>224</v>
+        <v>135</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R31" s="2"/>
       <c r="S31" t="s" s="2">
-        <v>22</v>
+        <v>223</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>22</v>
@@ -6320,10 +6552,10 @@
         <v>22</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>85</v>
@@ -6332,18 +6564,18 @@
         <v>22</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -6351,10 +6583,10 @@
       </c>
       <c r="F32" s="2"/>
       <c r="G32" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>22</v>
@@ -6366,15 +6598,17 @@
         <v>22</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M32" t="s" s="2">
         <v>229</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
         <v>22</v>
@@ -6423,30 +6657,30 @@
         <v>22</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -6457,7 +6691,7 @@
         <v>76</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>22</v>
@@ -6469,13 +6703,13 @@
         <v>22</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>87</v>
+        <v>235</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>88</v>
+        <v>161</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -6526,30 +6760,30 @@
         <v>22</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -6560,7 +6794,7 @@
         <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>22</v>
@@ -6572,13 +6806,13 @@
         <v>22</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -6617,42 +6851,42 @@
         <v>22</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE34" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -6660,10 +6894,10 @@
       </c>
       <c r="F35" s="2"/>
       <c r="G35" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>22</v>
@@ -6675,24 +6909,22 @@
         <v>22</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R35" s="2"/>
       <c r="S35" t="s" s="2">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>22</v>
@@ -6722,42 +6954,42 @@
         <v>22</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE35" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -6780,22 +7012,24 @@
         <v>22</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>231</v>
+        <v>134</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>232</v>
+        <v>135</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R36" s="2"/>
       <c r="S36" t="s" s="2">
-        <v>22</v>
+        <v>233</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>22</v>
@@ -6837,10 +7071,10 @@
         <v>22</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>85</v>
@@ -6849,18 +7083,18 @@
         <v>22</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>239</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>239</v>
+        <v>138</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6868,10 +7102,10 @@
       </c>
       <c r="F37" s="2"/>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>22</v>
@@ -6883,17 +7117,15 @@
         <v>22</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" t="s" s="2">
         <v>22</v>
@@ -6942,30 +7174,30 @@
         <v>22</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>239</v>
+        <v>138</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>244</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>245</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>245</v>
+        <v>126</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6976,7 +7208,7 @@
         <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>22</v>
@@ -6988,13 +7220,13 @@
         <v>22</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -7045,41 +7277,41 @@
         <v>22</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>246</v>
+        <v>130</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>22</v>
@@ -7091,17 +7323,15 @@
         <v>22</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>95</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" s="2"/>
       <c r="Q39" t="s" s="2">
         <v>22</v>
@@ -7138,46 +7368,44 @@
         <v>22</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE39" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>247</v>
+        <v>131</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
         <v>22</v>
       </c>
@@ -7186,7 +7414,7 @@
         <v>76</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>22</v>
@@ -7198,13 +7426,13 @@
         <v>22</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>249</v>
+        <v>92</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>250</v>
+        <v>126</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>251</v>
+        <v>132</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -7243,16 +7471,16 @@
         <v>22</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE40" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>99</v>
@@ -7272,13 +7500,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>252</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>252</v>
+        <v>133</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -7286,7 +7514,7 @@
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>85</v>
@@ -7298,29 +7526,27 @@
         <v>22</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>253</v>
+        <v>134</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>254</v>
+        <v>135</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>255</v>
+        <v>136</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="P41" s="2"/>
       <c r="Q41" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R41" s="2"/>
       <c r="S41" t="s" s="2">
-        <v>22</v>
+        <v>241</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>22</v>
@@ -7362,10 +7588,10 @@
         <v>22</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>252</v>
+        <v>133</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>85</v>
@@ -7374,18 +7600,18 @@
         <v>22</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>258</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>258</v>
+        <v>138</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -7393,7 +7619,7 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>85</v>
@@ -7408,13 +7634,13 @@
         <v>22</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>86</v>
+        <v>245</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -7465,7 +7691,7 @@
         <v>22</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
@@ -7477,18 +7703,18 @@
         <v>22</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -7511,15 +7737,17 @@
         <v>22</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
         <v>22</v>
@@ -7556,17 +7784,19 @@
         <v>22</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AD43" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="AE43" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>99</v>
+        <v>253</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>76</v>
@@ -7575,25 +7805,23 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>100</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D44" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
         <v>22</v>
       </c>
@@ -7614,17 +7842,15 @@
         <v>22</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>264</v>
+        <v>86</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>265</v>
+        <v>87</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
         <v>22</v>
@@ -7673,43 +7899,41 @@
         <v>22</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>22</v>
@@ -7721,15 +7945,17 @@
         <v>22</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>270</v>
+        <v>92</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>271</v>
+        <v>93</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>95</v>
+      </c>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
         <v>22</v>
@@ -7766,16 +7992,16 @@
         <v>22</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE45" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>99</v>
@@ -7787,7 +8013,7 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>100</v>
@@ -7795,15 +8021,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="D46" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="E46" t="s" s="2">
         <v>22</v>
       </c>
@@ -7824,13 +8052,13 @@
         <v>22</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
@@ -7881,30 +8109,30 @@
         <v>22</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>276</v>
+        <v>99</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7921,30 +8149,30 @@
         <v>22</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>168</v>
+        <v>267</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P47" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="R47" t="s" s="2">
-        <v>281</v>
-      </c>
+      <c r="R47" s="2"/>
       <c r="S47" t="s" s="2">
         <v>22</v>
       </c>
@@ -7964,13 +8192,13 @@
         <v>22</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>173</v>
+        <v>22</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>282</v>
+        <v>22</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>283</v>
+        <v>22</v>
       </c>
       <c r="AB47" t="s" s="2">
         <v>22</v>
@@ -7988,7 +8216,7 @@
         <v>22</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -8005,13 +8233,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -8031,21 +8259,19 @@
         <v>22</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>86</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>287</v>
-      </c>
+      <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
         <v>22</v>
       </c>
@@ -8093,7 +8319,7 @@
         <v>22</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>284</v>
+        <v>89</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -8105,18 +8331,18 @@
         <v>22</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -8127,7 +8353,7 @@
         <v>76</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>22</v>
@@ -8136,21 +8362,19 @@
         <v>22</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>289</v>
+        <v>126</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>290</v>
+        <v>132</v>
       </c>
       <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>291</v>
-      </c>
+      <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
         <v>22</v>
       </c>
@@ -8186,44 +8410,44 @@
         <v>22</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AD49" s="2"/>
       <c r="AE49" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>288</v>
+        <v>99</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>292</v>
+        <v>22</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="D50" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="E50" t="s" s="2">
         <v>22</v>
       </c>
@@ -8241,23 +8465,21 @@
         <v>22</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
         <v>22</v>
       </c>
@@ -8305,32 +8527,34 @@
         <v>22</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>293</v>
+        <v>99</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>126</v>
+        <v>282</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="D51" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="E51" t="s" s="2">
         <v>22</v>
       </c>
@@ -8339,7 +8563,7 @@
         <v>76</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>22</v>
@@ -8351,13 +8575,13 @@
         <v>22</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -8408,7 +8632,7 @@
         <v>22</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>76</v>
@@ -8425,13 +8649,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>130</v>
+        <v>287</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>130</v>
+        <v>287</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -8454,13 +8678,13 @@
         <v>22</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>86</v>
+        <v>267</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>87</v>
+        <v>288</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>88</v>
+        <v>289</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -8511,7 +8735,7 @@
         <v>22</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>76</v>
@@ -8528,13 +8752,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>131</v>
+        <v>291</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>131</v>
+        <v>291</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -8545,32 +8769,36 @@
         <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>22</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>126</v>
+        <v>292</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>132</v>
+        <v>293</v>
       </c>
       <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="Q53" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="R53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="S53" t="s" s="2">
         <v>22</v>
       </c>
@@ -8590,54 +8818,54 @@
         <v>22</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>22</v>
+        <v>297</v>
       </c>
       <c r="AB53" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE53" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>99</v>
+        <v>291</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="B54" t="s" s="2">
-        <v>133</v>
-      </c>
       <c r="C54" t="s" s="2">
-        <v>133</v>
+        <v>298</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8645,7 +8873,7 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>85</v>
@@ -8657,27 +8885,27 @@
         <v>22</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>135</v>
+        <v>299</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="P54" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="Q54" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R54" s="2"/>
       <c r="S54" t="s" s="2">
-        <v>299</v>
+        <v>22</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>22</v>
@@ -8719,10 +8947,10 @@
         <v>22</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>133</v>
+        <v>298</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>85</v>
@@ -8731,18 +8959,18 @@
         <v>22</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>138</v>
+        <v>302</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>138</v>
+        <v>302</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8750,7 +8978,7 @@
       </c>
       <c r="F55" s="2"/>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>85</v>
@@ -8762,10 +8990,10 @@
         <v>22</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>303</v>
@@ -8774,7 +9002,9 @@
         <v>304</v>
       </c>
       <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="Q55" t="s" s="2">
         <v>22</v>
       </c>
@@ -8822,7 +9052,7 @@
         <v>22</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>138</v>
+        <v>302</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
@@ -8831,7 +9061,7 @@
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>22</v>
+        <v>306</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8839,13 +9069,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>305</v>
+        <v>248</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>126</v>
+        <v>307</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>126</v>
+        <v>307</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8856,7 +9086,7 @@
         <v>76</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>22</v>
@@ -8865,19 +9095,23 @@
         <v>22</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="Q56" t="s" s="2">
         <v>22</v>
       </c>
@@ -8925,30 +9159,30 @@
         <v>22</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>126</v>
+        <v>307</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8959,7 +9193,7 @@
         <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>22</v>
@@ -8971,13 +9205,13 @@
         <v>22</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>87</v>
+        <v>264</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>88</v>
+        <v>265</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -9028,30 +9262,30 @@
         <v>22</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -9062,7 +9296,7 @@
         <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>22</v>
@@ -9074,13 +9308,13 @@
         <v>22</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -9119,42 +9353,42 @@
         <v>22</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE58" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -9162,10 +9396,10 @@
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>22</v>
@@ -9177,24 +9411,22 @@
         <v>22</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R59" s="2"/>
       <c r="S59" t="s" s="2">
-        <v>306</v>
+        <v>22</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>22</v>
@@ -9224,42 +9456,42 @@
         <v>22</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD59" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE59" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -9282,22 +9514,24 @@
         <v>22</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>310</v>
+        <v>135</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R60" s="2"/>
       <c r="S60" t="s" s="2">
-        <v>22</v>
+        <v>313</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>22</v>
@@ -9339,10 +9573,10 @@
         <v>22</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>85</v>
@@ -9351,7 +9585,7 @@
         <v>22</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -9359,10 +9593,10 @@
         <v>312</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>318</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>318</v>
+        <v>138</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -9370,10 +9604,10 @@
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>22</v>
@@ -9385,17 +9619,15 @@
         <v>22</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
         <v>22</v>
@@ -9444,30 +9676,30 @@
         <v>22</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>318</v>
+        <v>138</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>324</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>324</v>
+        <v>126</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -9478,7 +9710,7 @@
         <v>76</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>22</v>
@@ -9490,13 +9722,13 @@
         <v>22</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>87</v>
+        <v>285</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>88</v>
+        <v>286</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -9547,41 +9779,41 @@
         <v>22</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>22</v>
@@ -9593,17 +9825,15 @@
         <v>22</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>95</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
         <v>22</v>
@@ -9640,46 +9870,44 @@
         <v>22</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD63" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE63" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>326</v>
+        <v>131</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="D64" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
         <v>22</v>
       </c>
@@ -9688,7 +9916,7 @@
         <v>76</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>22</v>
@@ -9700,13 +9928,13 @@
         <v>22</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>328</v>
+        <v>92</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>329</v>
+        <v>126</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>330</v>
+        <v>132</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -9745,16 +9973,16 @@
         <v>22</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD64" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE64" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>99</v>
@@ -9774,13 +10002,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>331</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>331</v>
+        <v>133</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9788,7 +10016,7 @@
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -9800,19 +10028,19 @@
         <v>22</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>332</v>
+        <v>135</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>333</v>
+        <v>136</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>334</v>
+        <v>137</v>
       </c>
       <c r="P65" s="2"/>
       <c r="Q65" t="s" s="2">
@@ -9820,7 +10048,7 @@
       </c>
       <c r="R65" s="2"/>
       <c r="S65" t="s" s="2">
-        <v>22</v>
+        <v>320</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>22</v>
@@ -9862,30 +10090,30 @@
         <v>22</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>331</v>
+        <v>133</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>335</v>
+        <v>22</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>336</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>336</v>
+        <v>138</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9893,7 +10121,7 @@
       </c>
       <c r="F66" s="2"/>
       <c r="G66" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -9905,20 +10133,18 @@
         <v>22</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
         <v>22</v>
@@ -9943,13 +10169,13 @@
         <v>22</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>340</v>
+        <v>22</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>341</v>
+        <v>22</v>
       </c>
       <c r="AA66" t="s" s="2">
-        <v>342</v>
+        <v>22</v>
       </c>
       <c r="AB66" t="s" s="2">
         <v>22</v>
@@ -9967,7 +10193,7 @@
         <v>22</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>336</v>
+        <v>138</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>76</v>
@@ -9984,13 +10210,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -10001,7 +10227,7 @@
         <v>76</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>22</v>
@@ -10010,19 +10236,19 @@
         <v>22</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -10072,30 +10298,30 @@
         <v>22</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -10115,20 +10341,18 @@
         <v>22</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>86</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>349</v>
+        <v>87</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
         <v>22</v>
@@ -10177,7 +10401,7 @@
         <v>22</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>348</v>
+        <v>89</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>76</v>
@@ -10189,22 +10413,22 @@
         <v>22</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>126</v>
+        <v>339</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>126</v>
+        <v>339</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" t="s" s="2">
@@ -10223,15 +10447,17 @@
         <v>22</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>355</v>
+        <v>93</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>95</v>
+      </c>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
         <v>22</v>
@@ -10268,19 +10494,19 @@
         <v>22</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD69" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE69" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>76</v>
@@ -10289,7 +10515,7 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>100</v>
@@ -10297,15 +10523,17 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="D70" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="E70" t="s" s="2">
         <v>22</v>
       </c>
@@ -10314,7 +10542,7 @@
         <v>76</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>22</v>
@@ -10326,13 +10554,13 @@
         <v>22</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>86</v>
+        <v>342</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>87</v>
+        <v>343</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>88</v>
+        <v>344</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
@@ -10383,30 +10611,30 @@
         <v>22</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>131</v>
+        <v>345</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>131</v>
+        <v>345</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10417,7 +10645,7 @@
         <v>76</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>22</v>
@@ -10426,18 +10654,20 @@
         <v>22</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>126</v>
+        <v>346</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
         <v>22</v>
@@ -10474,42 +10704,42 @@
         <v>22</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD71" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE71" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>99</v>
+        <v>345</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>22</v>
+        <v>349</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>133</v>
+        <v>350</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>133</v>
+        <v>350</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -10517,7 +10747,7 @@
       </c>
       <c r="F72" s="2"/>
       <c r="G72" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
@@ -10529,19 +10759,19 @@
         <v>22</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>134</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>135</v>
+        <v>351</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>136</v>
+        <v>352</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>137</v>
+        <v>353</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" t="s" s="2">
@@ -10549,7 +10779,7 @@
       </c>
       <c r="R72" s="2"/>
       <c r="S72" t="s" s="2">
-        <v>353</v>
+        <v>22</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>22</v>
@@ -10567,13 +10797,13 @@
         <v>22</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>22</v>
+        <v>354</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>22</v>
+        <v>355</v>
       </c>
       <c r="AA72" t="s" s="2">
-        <v>22</v>
+        <v>356</v>
       </c>
       <c r="AB72" t="s" s="2">
         <v>22</v>
@@ -10591,10 +10821,10 @@
         <v>22</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>133</v>
+        <v>350</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
@@ -10603,18 +10833,18 @@
         <v>22</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>138</v>
+        <v>357</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>138</v>
+        <v>357</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10622,7 +10852,7 @@
       </c>
       <c r="F73" s="2"/>
       <c r="G73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -10634,10 +10864,10 @@
         <v>22</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>359</v>
@@ -10696,18 +10926,642 @@
         <v>22</v>
       </c>
       <c r="AG73" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="D74" s="2"/>
+      <c r="E74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F74" s="2"/>
+      <c r="G74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="P74" s="2"/>
+      <c r="Q74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R74" s="2"/>
+      <c r="S74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F75" s="2"/>
+      <c r="G75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R75" s="2"/>
+      <c r="S75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="D76" s="2"/>
+      <c r="E76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F76" s="2"/>
+      <c r="G76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R76" s="2"/>
+      <c r="S76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F77" s="2"/>
+      <c r="G77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R77" s="2"/>
+      <c r="S77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="D78" s="2"/>
+      <c r="E78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F78" s="2"/>
+      <c r="G78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="P78" s="2"/>
+      <c r="Q78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R78" s="2"/>
+      <c r="S78" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AH73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK73" t="s" s="2">
+      <c r="C79" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P79" s="2"/>
+      <c r="Q79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R79" s="2"/>
+      <c r="S79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK79" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3072" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2835" uniqueCount="368">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:29:14+05:30</t>
+    <t>2026-05-15T09:21:03+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -485,9 +485,11 @@
 SHALL never be populated.
 All attachment content SHALL be externalized into object storage
 and referenced using Attachment.url.
-If content originated as inline data/blob content and was later
-saved externally, the extension
-attachment-inlineDataSavedAsFile SHALL be used to indicate this.</t>
+If attachment content originated as inline data/blob content
+and was subsequently externalized into object storage, the
+Attachment SHALL carry the tag
+'inline-data-externalized-to-file' using the attachment-tag
+extension.</t>
   </si>
   <si>
     <t>Provides a consistent attachment handling strategy in which
@@ -519,27 +521,6 @@
     <t>Attachment.extension</t>
   </si>
   <si>
-    <t>Attachment.extension:inlineDataSavedAsFile</t>
-  </si>
-  <si>
-    <t>inlineDataSavedAsFile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/attachment-inlineDataSavedAsFile}
-</t>
-  </si>
-  <si>
-    <t>Indicates originally-inline content externalized into object storage</t>
-  </si>
-  <si>
-    <t>Indicates that the Attachment content was originally available
-as inline data/blob content but has been externalized and saved
-as a file in object storage, with the Attachment.url carrying
-the storage location.
-If this extension is absent, the content SHALL be assumed to
-have originated as an external file rather than inline data.</t>
-  </si>
-  <si>
     <t>Attachment.extension:tag</t>
   </si>
   <si>
@@ -553,10 +534,10 @@
     <t>Semantic categorization tag associated with the attachment</t>
   </si>
   <si>
-    <t>A categorization or tagging label associated with an Attachment.
+    <t>A categorization or semantic tag associated with an Attachment.
 This extension allows multiple tags to be associated with an
-Attachment for workflow, classification, indexing, or retrieval
-purposes.</t>
+Attachment for workflow, classification, indexing, retrieval,
+processing, or application behavior purposes.</t>
   </si>
   <si>
     <t>Attachment.extension:helperFile</t>
@@ -660,7 +641,9 @@
     <t>Object storage path or external attachment location</t>
   </si>
   <si>
-    <t>Reference/path to the externally stored attachment content.</t>
+    <t>Reference/path to the externally stored attachment content. Inline binary data in 
+Attachment.data SHALL NOT be populated. Inline content SHALL instead be persisted 
+externally, referenced using this url element, and tagged as 'inline-data-externalized-to-file'.</t>
   </si>
   <si>
     <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
@@ -765,44 +748,18 @@
     <t>element:Attachment</t>
   </si>
   <si>
-    <t>Path or filename of associated helper/supporting file</t>
-  </si>
-  <si>
-    <t>Specifies the path, filename, or storage reference of a helper/supporting
-file associated with the attachment.</t>
+    <t>Path, locator or filename of associated helper/supporting file</t>
+  </si>
+  <si>
+    <t>Specifies the path, locator, storage reference,
+or URL of a helper/supporting file associated
+with the attachment.</t>
   </si>
   <si>
     <t>The interpretation and usage of the helper file is dependent upon
 the attachment content type and consuming application.</t>
   </si>
   <si>
-    <t>attachment-inlineDataSavedAsFile</t>
-  </si>
-  <si>
-    <t>http://314e.com/fhir/StructureDefinition/attachment-inlineDataSavedAsFile</t>
-  </si>
-  <si>
-    <t>AttachmentInlineDataSavedAsFile</t>
-  </si>
-  <si>
-    <t>Attachment Inline Data Saved As File</t>
-  </si>
-  <si>
-    <t>Supports workflows in which inline binary content is externalized
-into object storage and referenced through Attachment.url.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Whether inline content was externalized to object storage</t>
-  </si>
-  <si>
-    <t>True indicates that the content was originally available as
-inline data/blob content and was saved as a file in object storage.</t>
-  </si>
-  <si>
     <t>attachment-tag</t>
   </si>
   <si>
@@ -822,11 +779,18 @@
 </t>
   </si>
   <si>
-    <t>Categorization tag for the attachment</t>
+    <t>Semantic categorization tag for the attachment</t>
   </si>
   <si>
     <t>Represents a semantic classification, workflow label,
-or categorization tag associated with the attachment.</t>
+behavioral indicator, or categorization tag associated
+with the attachment.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/attachment-tag</t>
   </si>
   <si>
     <t>quantity-314e</t>
@@ -884,6 +848,182 @@
   <si>
     <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/quantity-quantityString}
 </t>
+  </si>
+  <si>
+    <t>Original or display-oriented textual representation of the full quantity</t>
+  </si>
+  <si>
+    <t>Provides the original, source-oriented, or display-oriented textual
+representation of the complete quantity, including value and unit.
+This extension is intended for situations in which:
+- the original quantity representation cannot be cleanly decomposed
+  into computable Quantity elements,
+- the original source representation must be preserved for audit,
+  fidelity, or display purposes,
+- or the display representation differs from the computable form.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Quantity.value.extension</t>
+  </si>
+  <si>
+    <t>Quantity.value.extension:precision</t>
+  </si>
+  <si>
+    <t>precision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {quantity-precision}
+</t>
+  </si>
+  <si>
+    <t>Explicit precision of the numeric quantity value</t>
+  </si>
+  <si>
+    <t>Explicit precision of the numeric quantity value.
+This represents the number of significant decimal places intended
+for the quantity value, irrespective of how many decimal places
+are explicitly present in the decimal representation itself.
+The presence of this extension does not alter the underlying
+numeric value or computation semantics.</t>
+  </si>
+  <si>
+    <t>The presence of this extension does not change conformance expectations with regard to rendering and calculations that use the number - these are still based on the raw decimal value. Applications that perform calculations SHALL ensure that this extension is removed or updated to the correct precision value if the number is changed. Applications should consider using the exponential form (e.g. 2.10e3) on the raw decimal to manage significant figures, but should be mindful of human display when doing so.</t>
+  </si>
+  <si>
+    <t>Quantity.value.extension:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/quantity-valueString}
+</t>
+  </si>
+  <si>
+    <t>Original or display-oriented textual representation of the numeric value</t>
+  </si>
+  <si>
+    <t>Provides the original, source-oriented, or display-oriented textual
+representation of the numeric quantity value component.
+This extension may be used when:
+- the original formatting of the numeric value must be preserved,
+- the numeric representation contains significant formatting,
+- the value cannot be faithfully represented as a computable decimal,
+- or the original source representation is needed for display,
+  audit, or traceability purposes.</t>
+  </si>
+  <si>
+    <t>Quantity.value.value</t>
+  </si>
+  <si>
+    <t>Primitive value for decimal</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>decimal.value</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>quantity-quantityString</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/StructureDefinition/quantity-quantityString</t>
+  </si>
+  <si>
+    <t>QuantityQuantityString</t>
   </si>
   <si>
     <t>Quantity Quantity String</t>
@@ -900,64 +1040,29 @@
 and this extension if either representation is modified.</t>
   </si>
   <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Quantity.value.extension</t>
-  </si>
-  <si>
-    <t>Quantity.value.extension:precision</t>
-  </si>
-  <si>
-    <t>precision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {quantity-precision}
-</t>
-  </si>
-  <si>
-    <t>Explicit precision (number of significant decimal places)</t>
-  </si>
-  <si>
-    <t>Explicit precision of the number. This is the number of significant decimal places after the decimal point, irrespective of how many are actually present in the explicitly represented decimal.</t>
-  </si>
-  <si>
-    <t>The presence of this extension does not change conformance expectations with regard to rendering and calculations that use the number - these are still based on the raw decimal value. Applications that perform calculations SHALL ensure that this extension is removed or updated to the correct precision value if the number is changed. Applications should consider using the exponential form (e.g. 2.10e3) on the raw decimal to manage significant figures, but should be mindful of human display when doing so.</t>
-  </si>
-  <si>
-    <t>Quantity.value.extension:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/quantity-valueString}
-</t>
+    <t>Allows textual representation of a quantity where otherwise not possible to 
+represent as a string and the original quantity string cannot be separated into distinct value 
+and unit.
+Supports preservation of a display-oriented or source-oriented
+representation of a quantity.</t>
+  </si>
+  <si>
+    <t>element:Quantity</t>
+  </si>
+  <si>
+    <t>Original textual quantity representation</t>
+  </si>
+  <si>
+    <t>Carries the original source lexical representation of the full quantity, incuding value and unit.</t>
+  </si>
+  <si>
+    <t>quantity-valueString</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/StructureDefinition/quantity-valueString</t>
+  </si>
+  <si>
+    <t>QuantityValueString</t>
   </si>
   <si>
     <t>Quantity Value String</t>
@@ -975,116 +1080,6 @@
 and this extension if either representation is modified.</t>
   </si>
   <si>
-    <t>Quantity.value.value</t>
-  </si>
-  <si>
-    <t>Primitive value for decimal</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>decimal.value</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>quantity-quantityString</t>
-  </si>
-  <si>
-    <t>http://314e.com/fhir/StructureDefinition/quantity-quantityString</t>
-  </si>
-  <si>
-    <t>QuantityQuantityString</t>
-  </si>
-  <si>
-    <t>Allows textual representation of a quantity where otherwise not possible to 
-represent as a string and the original quantity string cannot be separated into distinct value 
-and unit.
-Supports preservation of a display-oriented or source-oriented
-representation of a quantity.</t>
-  </si>
-  <si>
-    <t>element:Quantity</t>
-  </si>
-  <si>
-    <t>Original textual quantity representation</t>
-  </si>
-  <si>
-    <t>Carries the original source lexical representation of the full quantity, incuding value and unit.</t>
-  </si>
-  <si>
-    <t>quantity-valueString</t>
-  </si>
-  <si>
-    <t>http://314e.com/fhir/StructureDefinition/quantity-valueString</t>
-  </si>
-  <si>
-    <t>QuantityValueString</t>
-  </si>
-  <si>
     <t>Allows representation of a quantity value as string.
 Supports preservation of the original source representation of a quantity value for 
 display or audit purposes.</t>
@@ -1191,9 +1186,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -1404,7 +1396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B238"/>
+  <dimension ref="A1:B216"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1924,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="67">
@@ -1932,7 +1924,7 @@
         <v>4</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="68">
@@ -1948,7 +1940,7 @@
         <v>8</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70">
@@ -1956,7 +1948,7 @@
         <v>10</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="71">
@@ -2010,7 +2002,7 @@
         <v>23</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78">
@@ -2018,7 +2010,7 @@
         <v>25</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="79">
@@ -2080,7 +2072,7 @@
         <v>128</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87">
@@ -2096,7 +2088,7 @@
         <v>2</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="89">
@@ -2104,7 +2096,7 @@
         <v>4</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90">
@@ -2120,7 +2112,7 @@
         <v>8</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="92">
@@ -2128,7 +2120,7 @@
         <v>10</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="93">
@@ -2190,7 +2182,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="101">
@@ -2252,7 +2244,7 @@
         <v>128</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="109">
@@ -2268,7 +2260,7 @@
         <v>2</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111">
@@ -2276,7 +2268,7 @@
         <v>4</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="112">
@@ -2292,7 +2284,7 @@
         <v>8</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114">
@@ -2300,7 +2292,7 @@
         <v>10</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="115">
@@ -2354,16 +2346,14 @@
         <v>23</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>166</v>
+        <v>241</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B122" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="B122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
@@ -2392,7 +2382,7 @@
         <v>32</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>126</v>
+        <v>242</v>
       </c>
     </row>
     <row r="127">
@@ -2400,7 +2390,7 @@
         <v>34</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>127</v>
+        <v>243</v>
       </c>
     </row>
     <row r="128">
@@ -2420,173 +2410,175 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>228</v>
+      <c r="A130" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B130" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B131" t="s" s="1">
-        <v>1</v>
+      <c r="A131" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>301</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>248</v>
+        <v>302</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>249</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>7</v>
+        <v>303</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>250</v>
+        <v>304</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>251</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B138" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>16</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>22</v>
+        <v>305</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>252</v>
+        <v>306</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B145" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>31</v>
+        <v>126</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>253</v>
+        <v>127</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>254</v>
+        <v>37</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>39</v>
+        <v>307</v>
       </c>
     </row>
     <row r="152">
@@ -2602,7 +2594,7 @@
         <v>2</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="154">
@@ -2610,7 +2602,7 @@
         <v>4</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="155">
@@ -2626,7 +2618,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="157">
@@ -2634,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>264</v>
+        <v>313</v>
       </c>
     </row>
     <row r="158">
@@ -2688,7 +2680,7 @@
         <v>23</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>265</v>
+        <v>314</v>
       </c>
     </row>
     <row r="165">
@@ -2806,7 +2798,7 @@
         <v>10</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>285</v>
+        <v>322</v>
       </c>
     </row>
     <row r="180">
@@ -2860,7 +2852,7 @@
         <v>23</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>286</v>
+        <v>323</v>
       </c>
     </row>
     <row r="187">
@@ -2868,7 +2860,7 @@
         <v>25</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="188">
@@ -2898,7 +2890,7 @@
         <v>32</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>126</v>
+        <v>325</v>
       </c>
     </row>
     <row r="192">
@@ -2906,7 +2898,7 @@
         <v>34</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>127</v>
+        <v>326</v>
       </c>
     </row>
     <row r="193">
@@ -2926,347 +2918,175 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>323</v>
+      <c r="A195" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B195" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B196" t="s" s="1">
-        <v>1</v>
+      <c r="A196" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>358</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>326</v>
+        <v>359</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>327</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>7</v>
+        <v>360</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>328</v>
+        <v>361</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>329</v>
+        <v>13</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B203" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>16</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>22</v>
+        <v>362</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>330</v>
+        <v>363</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B209" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B210" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>29</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>31</v>
+        <v>126</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>332</v>
+        <v>127</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>333</v>
+        <v>37</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B217" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B218" t="s" s="2">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B219" t="s" s="2">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B221" t="s" s="2">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B222" t="s" s="2">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B223" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B224" s="2"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B228" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B231" s="2"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="B238" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -3276,13 +3096,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK79"/>
+  <dimension ref="A1:AK73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="28.51953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="36.953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.7265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.57421875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.0859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="18.578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="12.328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="11.10546875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -5011,7 +4831,7 @@
         <v>76</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>22</v>
@@ -5116,7 +4936,7 @@
         <v>76</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>22</v>
@@ -5208,11 +5028,9 @@
         <v>167</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
         <v>22</v>
       </c>
@@ -5230,19 +5048,21 @@
         <v>22</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
         <v>22</v>
       </c>
@@ -5254,7 +5074,7 @@
         <v>22</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>22</v>
+        <v>172</v>
       </c>
       <c r="V19" t="s" s="2">
         <v>22</v>
@@ -5266,13 +5086,13 @@
         <v>22</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>22</v>
+        <v>173</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="AB19" t="s" s="2">
         <v>22</v>
@@ -5290,19 +5110,19 @@
         <v>22</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
@@ -5310,10 +5130,10 @@
         <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -5336,17 +5156,17 @@
         <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q20" t="s" s="2">
         <v>22</v>
@@ -5359,7 +5179,7 @@
         <v>22</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="V20" t="s" s="2">
         <v>22</v>
@@ -5371,13 +5191,13 @@
         <v>22</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AB20" t="s" s="2">
         <v>22</v>
@@ -5395,7 +5215,7 @@
         <v>22</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>76</v>
@@ -5415,10 +5235,10 @@
         <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -5429,7 +5249,7 @@
         <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>22</v>
@@ -5438,20 +5258,22 @@
         <v>22</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P21" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="Q21" t="s" s="2">
         <v>22</v>
@@ -5464,7 +5286,7 @@
         <v>22</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>185</v>
+        <v>22</v>
       </c>
       <c r="V21" t="s" s="2">
         <v>22</v>
@@ -5476,13 +5298,13 @@
         <v>22</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>187</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="AB21" t="s" s="2">
         <v>22</v>
@@ -5500,7 +5322,7 @@
         <v>22</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>76</v>
@@ -5520,10 +5342,10 @@
         <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -5531,10 +5353,10 @@
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>22</v>
@@ -5543,22 +5365,22 @@
         <v>22</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P22" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q22" t="s" s="2">
         <v>22</v>
@@ -5571,7 +5393,7 @@
         <v>22</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="V22" t="s" s="2">
         <v>22</v>
@@ -5607,7 +5429,7 @@
         <v>22</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>76</v>
@@ -5627,10 +5449,10 @@
         <v>143</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -5638,7 +5460,7 @@
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>85</v>
@@ -5653,19 +5475,19 @@
         <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q23" t="s" s="2">
         <v>22</v>
@@ -5678,7 +5500,7 @@
         <v>22</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>201</v>
+        <v>22</v>
       </c>
       <c r="V23" t="s" s="2">
         <v>22</v>
@@ -5714,7 +5536,7 @@
         <v>22</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>76</v>
@@ -5734,10 +5556,10 @@
         <v>143</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -5760,7 +5582,7 @@
         <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>204</v>
@@ -5821,7 +5643,7 @@
         <v>22</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>76</v>
@@ -5867,7 +5689,7 @@
         <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>190</v>
+        <v>86</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>209</v>
@@ -5875,11 +5697,9 @@
       <c r="N25" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="O25" t="s" s="2">
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="P25" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="Q25" t="s" s="2">
         <v>22</v>
@@ -5892,7 +5712,7 @@
         <v>22</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="V25" t="s" s="2">
         <v>22</v>
@@ -5974,7 +5794,7 @@
         <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>214</v>
@@ -5997,7 +5817,7 @@
         <v>22</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>217</v>
+        <v>22</v>
       </c>
       <c r="V26" t="s" s="2">
         <v>22</v>
@@ -6050,13 +5870,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>143</v>
+        <v>217</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>218</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>218</v>
+        <v>126</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -6067,7 +5887,7 @@
         <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>22</v>
@@ -6076,21 +5896,19 @@
         <v>22</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O27" s="2"/>
-      <c r="P27" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="P27" s="2"/>
       <c r="Q27" t="s" s="2">
         <v>22</v>
       </c>
@@ -6138,30 +5956,30 @@
         <v>22</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>218</v>
+        <v>126</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -6172,7 +5990,7 @@
         <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>22</v>
@@ -6184,13 +6002,13 @@
         <v>22</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>225</v>
+        <v>87</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>226</v>
+        <v>88</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -6241,30 +6059,30 @@
         <v>22</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -6275,7 +6093,7 @@
         <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>22</v>
@@ -6287,13 +6105,13 @@
         <v>22</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -6332,42 +6150,42 @@
         <v>22</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -6375,10 +6193,10 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>22</v>
@@ -6390,22 +6208,24 @@
         <v>22</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R30" s="2"/>
       <c r="S30" t="s" s="2">
-        <v>22</v>
+        <v>218</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>22</v>
@@ -6435,42 +6255,42 @@
         <v>22</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -6493,16 +6313,16 @@
         <v>22</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
@@ -6510,7 +6330,7 @@
       </c>
       <c r="R31" s="2"/>
       <c r="S31" t="s" s="2">
-        <v>223</v>
+        <v>22</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>22</v>
@@ -6552,10 +6372,10 @@
         <v>22</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>85</v>
@@ -6564,18 +6384,18 @@
         <v>22</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -6583,10 +6403,10 @@
       </c>
       <c r="F32" s="2"/>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>22</v>
@@ -6598,17 +6418,15 @@
         <v>22</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
         <v>22</v>
@@ -6657,30 +6475,30 @@
         <v>22</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -6691,7 +6509,7 @@
         <v>76</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>22</v>
@@ -6703,13 +6521,13 @@
         <v>22</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -6760,30 +6578,30 @@
         <v>22</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -6794,7 +6612,7 @@
         <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>22</v>
@@ -6806,13 +6624,13 @@
         <v>22</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -6851,42 +6669,42 @@
         <v>22</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE34" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -6894,10 +6712,10 @@
       </c>
       <c r="F35" s="2"/>
       <c r="G35" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>22</v>
@@ -6909,22 +6727,24 @@
         <v>22</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="P35" s="2"/>
       <c r="Q35" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R35" s="2"/>
       <c r="S35" t="s" s="2">
-        <v>22</v>
+        <v>228</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>22</v>
@@ -6954,42 +6774,42 @@
         <v>22</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE35" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -7012,24 +6832,22 @@
         <v>22</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>135</v>
+        <v>233</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R36" s="2"/>
       <c r="S36" t="s" s="2">
-        <v>233</v>
+        <v>22</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>22</v>
@@ -7047,13 +6865,11 @@
         <v>22</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="Z36" s="2"/>
       <c r="AA36" t="s" s="2">
-        <v>22</v>
+        <v>236</v>
       </c>
       <c r="AB36" t="s" s="2">
         <v>22</v>
@@ -7071,10 +6887,10 @@
         <v>22</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>85</v>
@@ -7083,18 +6899,18 @@
         <v>22</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -7102,10 +6918,10 @@
       </c>
       <c r="F37" s="2"/>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>22</v>
@@ -7117,15 +6933,17 @@
         <v>22</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P37" s="2"/>
       <c r="Q37" t="s" s="2">
         <v>22</v>
@@ -7174,30 +6992,30 @@
         <v>22</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>83</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -7208,7 +7026,7 @@
         <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>22</v>
@@ -7220,13 +7038,13 @@
         <v>22</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>243</v>
+        <v>87</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -7277,41 +7095,41 @@
         <v>22</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>130</v>
+        <v>249</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>130</v>
+        <v>249</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>22</v>
@@ -7323,15 +7141,17 @@
         <v>22</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>95</v>
+      </c>
       <c r="P39" s="2"/>
       <c r="Q39" t="s" s="2">
         <v>22</v>
@@ -7368,44 +7188,46 @@
         <v>22</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE39" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="D40" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="E40" t="s" s="2">
         <v>22</v>
       </c>
@@ -7414,7 +7236,7 @@
         <v>76</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>22</v>
@@ -7426,13 +7248,13 @@
         <v>22</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>92</v>
+        <v>252</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>126</v>
+        <v>253</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -7471,16 +7293,16 @@
         <v>22</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE40" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>99</v>
@@ -7500,13 +7322,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -7514,7 +7336,7 @@
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>85</v>
@@ -7526,27 +7348,29 @@
         <v>22</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>135</v>
+        <v>257</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="P41" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="Q41" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R41" s="2"/>
       <c r="S41" t="s" s="2">
-        <v>241</v>
+        <v>22</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>22</v>
@@ -7588,10 +7412,10 @@
         <v>22</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>85</v>
@@ -7600,18 +7424,18 @@
         <v>22</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>138</v>
+        <v>261</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>138</v>
+        <v>261</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -7619,7 +7443,7 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>85</v>
@@ -7634,13 +7458,13 @@
         <v>22</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>245</v>
+        <v>86</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -7691,7 +7515,7 @@
         <v>22</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
@@ -7703,18 +7527,18 @@
         <v>22</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -7737,17 +7561,15 @@
         <v>22</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
         <v>22</v>
@@ -7784,19 +7606,17 @@
         <v>22</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AD43" s="2"/>
       <c r="AE43" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>253</v>
+        <v>99</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>76</v>
@@ -7805,23 +7625,25 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>258</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="D44" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="E44" t="s" s="2">
         <v>22</v>
       </c>
@@ -7842,15 +7664,17 @@
         <v>22</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>86</v>
+        <v>267</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>87</v>
+        <v>268</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
         <v>22</v>
@@ -7899,41 +7723,43 @@
         <v>22</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="D45" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="E45" t="s" s="2">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>22</v>
@@ -7945,17 +7771,15 @@
         <v>22</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>92</v>
+        <v>273</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>93</v>
+        <v>274</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>95</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
         <v>22</v>
@@ -7992,16 +7816,16 @@
         <v>22</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE45" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>99</v>
@@ -8013,7 +7837,7 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>100</v>
@@ -8021,17 +7845,15 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
         <v>22</v>
       </c>
@@ -8052,13 +7874,13 @@
         <v>22</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
@@ -8109,30 +7931,30 @@
         <v>22</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>99</v>
+        <v>279</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -8149,30 +7971,30 @@
         <v>22</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>267</v>
+        <v>168</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="R47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="S47" t="s" s="2">
         <v>22</v>
       </c>
@@ -8192,13 +8014,13 @@
         <v>22</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>22</v>
+        <v>173</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>22</v>
+        <v>285</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>22</v>
+        <v>286</v>
       </c>
       <c r="AB47" t="s" s="2">
         <v>22</v>
@@ -8216,7 +8038,7 @@
         <v>22</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -8233,13 +8055,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -8259,19 +8081,21 @@
         <v>22</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>86</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="Q48" t="s" s="2">
         <v>22</v>
       </c>
@@ -8319,7 +8143,7 @@
         <v>22</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>89</v>
+        <v>287</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -8331,18 +8155,18 @@
         <v>22</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -8353,7 +8177,7 @@
         <v>76</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>22</v>
@@ -8362,19 +8186,21 @@
         <v>22</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>126</v>
+        <v>292</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>132</v>
+        <v>293</v>
       </c>
       <c r="O49" s="2"/>
-      <c r="P49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="Q49" t="s" s="2">
         <v>22</v>
       </c>
@@ -8410,44 +8236,44 @@
         <v>22</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AD49" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="AE49" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>99</v>
+        <v>291</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>22</v>
+        <v>295</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="D50" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
         <v>22</v>
       </c>
@@ -8465,21 +8291,23 @@
         <v>22</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>278</v>
+        <v>168</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="P50" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="Q50" t="s" s="2">
         <v>22</v>
       </c>
@@ -8527,34 +8355,32 @@
         <v>22</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>99</v>
+        <v>296</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>282</v>
+        <v>126</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
         <v>22</v>
       </c>
@@ -8563,7 +8389,7 @@
         <v>76</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>22</v>
@@ -8575,13 +8401,13 @@
         <v>22</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -8632,7 +8458,7 @@
         <v>22</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>76</v>
@@ -8649,13 +8475,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>287</v>
+        <v>130</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>287</v>
+        <v>130</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -8678,13 +8504,13 @@
         <v>22</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>267</v>
+        <v>86</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>288</v>
+        <v>87</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>289</v>
+        <v>88</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -8735,7 +8561,7 @@
         <v>22</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>290</v>
+        <v>89</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>76</v>
@@ -8752,13 +8578,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>291</v>
+        <v>131</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>291</v>
+        <v>131</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -8769,36 +8595,32 @@
         <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>22</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>173</v>
+        <v>92</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>292</v>
+        <v>126</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>293</v>
+        <v>132</v>
       </c>
       <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>294</v>
-      </c>
+      <c r="P53" s="2"/>
       <c r="Q53" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="R53" t="s" s="2">
-        <v>295</v>
-      </c>
+      <c r="R53" s="2"/>
       <c r="S53" t="s" s="2">
         <v>22</v>
       </c>
@@ -8818,54 +8640,54 @@
         <v>22</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>296</v>
+        <v>22</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>297</v>
+        <v>22</v>
       </c>
       <c r="AB53" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE53" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>291</v>
+        <v>99</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>298</v>
+        <v>133</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>298</v>
+        <v>133</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8873,7 +8695,7 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>85</v>
@@ -8885,27 +8707,27 @@
         <v>22</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R54" s="2"/>
       <c r="S54" t="s" s="2">
-        <v>22</v>
+        <v>302</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>22</v>
@@ -8947,10 +8769,10 @@
         <v>22</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>298</v>
+        <v>133</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>85</v>
@@ -8959,18 +8781,18 @@
         <v>22</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>302</v>
+        <v>138</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>302</v>
+        <v>138</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8978,7 +8800,7 @@
       </c>
       <c r="F55" s="2"/>
       <c r="G55" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>85</v>
@@ -8990,21 +8812,19 @@
         <v>22</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>305</v>
-      </c>
+      <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
         <v>22</v>
       </c>
@@ -9052,7 +8872,7 @@
         <v>22</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>302</v>
+        <v>138</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
@@ -9061,7 +8881,7 @@
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>306</v>
+        <v>22</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -9069,13 +8889,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>248</v>
+        <v>310</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>307</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>307</v>
+        <v>126</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -9086,7 +8906,7 @@
         <v>76</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>22</v>
@@ -9095,23 +8915,19 @@
         <v>22</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
       <c r="Q56" t="s" s="2">
         <v>22</v>
       </c>
@@ -9159,30 +8975,30 @@
         <v>22</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>307</v>
+        <v>126</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -9193,7 +9009,7 @@
         <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>22</v>
@@ -9205,13 +9021,13 @@
         <v>22</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>264</v>
+        <v>87</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>265</v>
+        <v>88</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -9262,30 +9078,30 @@
         <v>22</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -9296,7 +9112,7 @@
         <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>22</v>
@@ -9308,13 +9124,13 @@
         <v>22</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -9353,42 +9169,42 @@
         <v>22</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE58" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -9396,10 +9212,10 @@
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>22</v>
@@ -9411,22 +9227,24 @@
         <v>22</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R59" s="2"/>
       <c r="S59" t="s" s="2">
-        <v>22</v>
+        <v>311</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>22</v>
@@ -9456,42 +9274,42 @@
         <v>22</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD59" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE59" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -9514,24 +9332,22 @@
         <v>22</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>135</v>
+        <v>317</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R60" s="2"/>
       <c r="S60" t="s" s="2">
-        <v>313</v>
+        <v>22</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>22</v>
@@ -9573,10 +9389,10 @@
         <v>22</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>85</v>
@@ -9585,18 +9401,18 @@
         <v>22</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>138</v>
+        <v>325</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>138</v>
+        <v>325</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -9604,10 +9420,10 @@
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>22</v>
@@ -9619,15 +9435,17 @@
         <v>22</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
         <v>22</v>
@@ -9676,19 +9494,19 @@
         <v>22</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>138</v>
+        <v>325</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>83</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62">
@@ -9696,10 +9514,10 @@
         <v>319</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>126</v>
+        <v>331</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>126</v>
+        <v>331</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -9710,7 +9528,7 @@
         <v>76</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>22</v>
@@ -9722,13 +9540,13 @@
         <v>22</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>285</v>
+        <v>87</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>286</v>
+        <v>88</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -9779,19 +9597,19 @@
         <v>22</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
@@ -9799,21 +9617,21 @@
         <v>319</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>130</v>
+        <v>332</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>130</v>
+        <v>332</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>22</v>
@@ -9825,15 +9643,17 @@
         <v>22</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>95</v>
+      </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
         <v>22</v>
@@ -9870,31 +9690,31 @@
         <v>22</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD63" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE63" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -9902,12 +9722,14 @@
         <v>319</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>131</v>
+        <v>333</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="D64" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="D64" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="E64" t="s" s="2">
         <v>22</v>
       </c>
@@ -9916,7 +9738,7 @@
         <v>76</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>22</v>
@@ -9928,13 +9750,13 @@
         <v>22</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>92</v>
+        <v>335</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>126</v>
+        <v>336</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>132</v>
+        <v>337</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -9973,16 +9795,16 @@
         <v>22</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD64" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE64" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>99</v>
@@ -10005,10 +9827,10 @@
         <v>319</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>133</v>
+        <v>338</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>133</v>
+        <v>338</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -10016,7 +9838,7 @@
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10028,19 +9850,19 @@
         <v>22</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>135</v>
+        <v>339</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>136</v>
+        <v>340</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>137</v>
+        <v>341</v>
       </c>
       <c r="P65" s="2"/>
       <c r="Q65" t="s" s="2">
@@ -10048,7 +9870,7 @@
       </c>
       <c r="R65" s="2"/>
       <c r="S65" t="s" s="2">
-        <v>320</v>
+        <v>22</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>22</v>
@@ -10090,19 +9912,19 @@
         <v>22</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>133</v>
+        <v>338</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>22</v>
+        <v>342</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66">
@@ -10110,10 +9932,10 @@
         <v>319</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>138</v>
+        <v>343</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>138</v>
+        <v>343</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -10121,7 +9943,7 @@
       </c>
       <c r="F66" s="2"/>
       <c r="G66" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10133,18 +9955,20 @@
         <v>22</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
         <v>22</v>
@@ -10169,13 +9993,13 @@
         <v>22</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>22</v>
+        <v>235</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>22</v>
+        <v>347</v>
       </c>
       <c r="AA66" t="s" s="2">
-        <v>22</v>
+        <v>348</v>
       </c>
       <c r="AB66" t="s" s="2">
         <v>22</v>
@@ -10193,7 +10017,7 @@
         <v>22</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>138</v>
+        <v>343</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>76</v>
@@ -10210,13 +10034,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -10227,7 +10051,7 @@
         <v>76</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>22</v>
@@ -10236,19 +10060,19 @@
         <v>22</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -10298,30 +10122,30 @@
         <v>22</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -10341,18 +10165,20 @@
         <v>22</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>86</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>87</v>
+        <v>355</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
         <v>22</v>
@@ -10401,7 +10227,7 @@
         <v>22</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>354</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>76</v>
@@ -10413,22 +10239,22 @@
         <v>22</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>339</v>
+        <v>126</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>339</v>
+        <v>126</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" t="s" s="2">
@@ -10447,17 +10273,15 @@
         <v>22</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>93</v>
+        <v>361</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>95</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
         <v>22</v>
@@ -10494,19 +10318,19 @@
         <v>22</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD69" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE69" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>76</v>
@@ -10515,7 +10339,7 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>100</v>
@@ -10523,17 +10347,15 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="D70" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
         <v>22</v>
       </c>
@@ -10542,7 +10364,7 @@
         <v>76</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>22</v>
@@ -10554,13 +10376,13 @@
         <v>22</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>342</v>
+        <v>86</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>343</v>
+        <v>87</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>344</v>
+        <v>88</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
@@ -10611,30 +10433,30 @@
         <v>22</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>345</v>
+        <v>131</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>345</v>
+        <v>131</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10645,7 +10467,7 @@
         <v>76</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>22</v>
@@ -10654,20 +10476,18 @@
         <v>22</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>346</v>
+        <v>126</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
         <v>22</v>
@@ -10704,42 +10524,42 @@
         <v>22</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD71" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE71" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>345</v>
+        <v>99</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>349</v>
+        <v>22</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>350</v>
+        <v>133</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>350</v>
+        <v>133</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -10747,7 +10567,7 @@
       </c>
       <c r="F72" s="2"/>
       <c r="G72" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
@@ -10759,19 +10579,19 @@
         <v>22</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>134</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>351</v>
+        <v>135</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>352</v>
+        <v>136</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>353</v>
+        <v>137</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" t="s" s="2">
@@ -10779,7 +10599,7 @@
       </c>
       <c r="R72" s="2"/>
       <c r="S72" t="s" s="2">
-        <v>22</v>
+        <v>359</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>22</v>
@@ -10797,13 +10617,13 @@
         <v>22</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>354</v>
+        <v>22</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>355</v>
+        <v>22</v>
       </c>
       <c r="AA72" t="s" s="2">
-        <v>356</v>
+        <v>22</v>
       </c>
       <c r="AB72" t="s" s="2">
         <v>22</v>
@@ -10821,10 +10641,10 @@
         <v>22</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>350</v>
+        <v>133</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
@@ -10833,18 +10653,18 @@
         <v>22</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>357</v>
+        <v>138</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>357</v>
+        <v>138</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10852,7 +10672,7 @@
       </c>
       <c r="F73" s="2"/>
       <c r="G73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -10864,19 +10684,19 @@
         <v>22</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>358</v>
+        <v>232</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -10926,7 +10746,7 @@
         <v>22</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>357</v>
+        <v>138</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>76</v>
@@ -10938,630 +10758,6 @@
         <v>22</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="D74" s="2"/>
-      <c r="E74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F74" s="2"/>
-      <c r="G74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="P74" s="2"/>
-      <c r="Q74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R74" s="2"/>
-      <c r="S74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="D75" s="2"/>
-      <c r="E75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F75" s="2"/>
-      <c r="G75" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R75" s="2"/>
-      <c r="S75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="D76" s="2"/>
-      <c r="E76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F76" s="2"/>
-      <c r="G76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R76" s="2"/>
-      <c r="S76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="D77" s="2"/>
-      <c r="E77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F77" s="2"/>
-      <c r="G77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R77" s="2"/>
-      <c r="S77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="D78" s="2"/>
-      <c r="E78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F78" s="2"/>
-      <c r="G78" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="P78" s="2"/>
-      <c r="Q78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R78" s="2"/>
-      <c r="S78" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="D79" s="2"/>
-      <c r="E79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F79" s="2"/>
-      <c r="G79" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="P79" s="2"/>
-      <c r="Q79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R79" s="2"/>
-      <c r="S79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK79" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5355" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5424" uniqueCount="694">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T07:30:07+05:30</t>
+    <t>2026-05-16T10:04:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1713,11 +1713,12 @@
     <t>ServiceRequest.category</t>
   </si>
   <si>
-    <t>High-level category classification for the requested service</t>
-  </si>
-  <si>
-    <t>Categorizes the requested service into a standardized
-high-level clinical service domain.</t>
+    <t>Operational procedure/service categories</t>
+  </si>
+  <si>
+    <t>Broad and optional subcategory classifications used
+for workflow, routing, analytics, and operational
+grouping of ServiceRequest resources.</t>
   </si>
   <si>
     <t>There may be multiple axis of categorization depending on the context or use case for retrieving or displaying the resource.  The level of granularity is defined by the category concepts in the value set.</t>
@@ -1726,7 +1727,13 @@
     <t>Used for filtering what service request are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://314e.com/fhir/ValueSet/servicerequest-category-314e</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Classification of the requested service.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -1751,6 +1758,38 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-servicerequest-category</t>
   </si>
   <si>
+    <t>ServiceRequest.category:broadCategory</t>
+  </si>
+  <si>
+    <t>broadCategory</t>
+  </si>
+  <si>
+    <t>Required broad procedure/service category</t>
+  </si>
+  <si>
+    <t>Top-level operational classification of the requested
+service or procedure.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-broad-314e</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category:subCategory</t>
+  </si>
+  <si>
+    <t>subCategory</t>
+  </si>
+  <si>
+    <t>Optional detailed subcategory</t>
+  </si>
+  <si>
+    <t>More granular operational sub-classification of the
+requested service or procedure.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-subcategory-314e</t>
+  </si>
+  <si>
     <t>ServiceRequest.priority</t>
   </si>
   <si>
@@ -1893,9 +1932,6 @@
   </si>
   <si>
     <t>For information from the medical record intended to support the delivery of the requested services, use the `supportingInformation` element.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codified order entry details which are based on order context.</t>
@@ -4596,7 +4632,7 @@
         <v>2</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
     </row>
     <row r="282">
@@ -4604,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>672</v>
+        <v>683</v>
       </c>
     </row>
     <row r="283">
@@ -4620,7 +4656,7 @@
         <v>8</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>673</v>
+        <v>684</v>
       </c>
     </row>
     <row r="285">
@@ -4628,7 +4664,7 @@
         <v>10</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>674</v>
+        <v>685</v>
       </c>
     </row>
     <row r="286">
@@ -4682,7 +4718,7 @@
         <v>23</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>675</v>
+        <v>686</v>
       </c>
     </row>
     <row r="293">
@@ -4726,7 +4762,7 @@
         <v>34</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>676</v>
+        <v>687</v>
       </c>
     </row>
     <row r="299">
@@ -4752,13 +4788,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK145"/>
+  <dimension ref="A1:AK147"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.7265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.640625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="30.87890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="12.8671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="38.546875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -15308,17 +15344,19 @@
         <v>22</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z101" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="AA101" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AB101" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AD101" s="2"/>
       <c r="AE101" t="s" s="2">
@@ -15348,13 +15386,13 @@
         <v>410</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>508</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E102" t="s" s="2">
         <v>22</v>
@@ -15379,10 +15417,10 @@
         <v>232</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>511</v>
@@ -15416,10 +15454,10 @@
         <v>173</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AB102" t="s" s="2">
         <v>22</v>
@@ -15457,24 +15495,26 @@
         <v>410</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="D103" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="E103" t="s" s="2">
         <v>22</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="J103" t="s" s="2">
         <v>22</v>
@@ -15483,22 +15523,24 @@
         <v>107</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O103" s="2"/>
-      <c r="P103" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="Q103" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="R103" t="s" s="2">
-        <v>524</v>
-      </c>
+      <c r="R103" s="2"/>
       <c r="S103" t="s" s="2">
         <v>22</v>
       </c>
@@ -15520,11 +15562,9 @@
       <c r="Y103" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Z103" t="s" s="2">
-        <v>525</v>
-      </c>
+      <c r="Z103" s="2"/>
       <c r="AA103" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AB103" t="s" s="2">
         <v>22</v>
@@ -15542,13 +15582,13 @@
         <v>22</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>22</v>
@@ -15562,12 +15602,14 @@
         <v>410</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="D104" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="E104" t="s" s="2">
         <v>22</v>
       </c>
@@ -15579,62 +15621,58 @@
         <v>85</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>528</v>
+        <v>232</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="P104" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Q104" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R104" s="2"/>
+      <c r="S104" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Z104" s="2"/>
+      <c r="AA104" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="Q104" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R104" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>22</v>
-      </c>
       <c r="AB104" t="s" s="2">
         <v>22</v>
       </c>
@@ -15651,13 +15689,13 @@
         <v>22</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>22</v>
@@ -15671,24 +15709,24 @@
         <v>410</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
-        <v>535</v>
+        <v>22</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="J105" t="s" s="2">
         <v>22</v>
@@ -15697,22 +15735,22 @@
         <v>107</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" s="2"/>
       <c r="Q105" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="R105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="S105" t="s" s="2">
         <v>22</v>
       </c>
@@ -15732,11 +15770,13 @@
         <v>22</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Z105" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="AA105" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AB105" t="s" s="2">
         <v>22</v>
@@ -15754,7 +15794,7 @@
         <v>22</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>76</v>
@@ -15763,7 +15803,7 @@
         <v>85</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>540</v>
+        <v>22</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>83</v>
@@ -15774,10 +15814,10 @@
         <v>410</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -15794,26 +15834,32 @@
         <v>22</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>86</v>
+        <v>540</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>87</v>
+        <v>541</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="O106" s="2"/>
-      <c r="P106" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="Q106" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="R106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="S106" t="s" s="2">
         <v>22</v>
       </c>
@@ -15857,7 +15903,7 @@
         <v>22</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>89</v>
+        <v>539</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>76</v>
@@ -15869,7 +15915,7 @@
         <v>22</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="107">
@@ -15877,42 +15923,42 @@
         <v>410</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
-        <v>91</v>
+        <v>547</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>22</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>92</v>
+        <v>232</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>93</v>
+        <v>548</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>94</v>
+        <v>549</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>95</v>
+        <v>550</v>
       </c>
       <c r="P107" s="2"/>
       <c r="Q107" t="s" s="2">
@@ -15938,43 +15984,41 @@
         <v>22</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="Z107" s="2"/>
       <c r="AA107" t="s" s="2">
-        <v>22</v>
+        <v>551</v>
       </c>
       <c r="AB107" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD107" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE107" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>99</v>
+        <v>546</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>22</v>
+        <v>552</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108">
@@ -15982,14 +16026,12 @@
         <v>410</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="D108" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
         <v>22</v>
       </c>
@@ -16010,17 +16052,15 @@
         <v>22</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>545</v>
+        <v>86</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>546</v>
+        <v>87</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
         <v>22</v>
@@ -16069,19 +16109,19 @@
         <v>22</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>540</v>
+        <v>22</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109">
@@ -16089,14 +16129,14 @@
         <v>410</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" t="s" s="2">
@@ -16112,23 +16152,21 @@
         <v>22</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>550</v>
+        <v>92</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>551</v>
+        <v>93</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>552</v>
+        <v>94</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="P109" s="2"/>
       <c r="Q109" t="s" s="2">
         <v>22</v>
       </c>
@@ -16164,19 +16202,19 @@
         <v>22</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD109" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE109" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>555</v>
+        <v>99</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>76</v>
@@ -16188,7 +16226,7 @@
         <v>22</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110">
@@ -16196,12 +16234,14 @@
         <v>410</v>
       </c>
       <c r="B110" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="D110" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="C110" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
         <v>22</v>
       </c>
@@ -16219,23 +16259,21 @@
         <v>22</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>86</v>
+        <v>557</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="P110" t="s" s="2">
         <v>560</v>
       </c>
+      <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
         <v>22</v>
       </c>
@@ -16283,19 +16321,19 @@
         <v>22</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>561</v>
+        <v>99</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>22</v>
+        <v>552</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="111">
@@ -16303,14 +16341,14 @@
         <v>410</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
-        <v>563</v>
+        <v>22</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" t="s" s="2">
@@ -16329,18 +16367,20 @@
         <v>107</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>232</v>
+        <v>562</v>
       </c>
       <c r="M111" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="O111" t="s" s="2">
+      <c r="P111" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="P111" s="2"/>
       <c r="Q111" t="s" s="2">
         <v>22</v>
       </c>
@@ -16364,31 +16404,31 @@
         <v>22</v>
       </c>
       <c r="Y111" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG111" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -16397,7 +16437,7 @@
         <v>77</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>570</v>
+        <v>22</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>83</v>
@@ -16408,10 +16448,10 @@
         <v>410</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -16434,17 +16474,19 @@
         <v>107</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="P112" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="Q112" t="s" s="2">
         <v>22</v>
@@ -16493,7 +16535,7 @@
         <v>22</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>76</v>
@@ -16513,24 +16555,24 @@
         <v>410</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
-        <v>22</v>
+        <v>575</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="J113" t="s" s="2">
         <v>22</v>
@@ -16539,15 +16581,17 @@
         <v>107</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N113" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O113" s="2"/>
       <c r="P113" s="2"/>
       <c r="Q113" t="s" s="2">
         <v>22</v>
@@ -16572,13 +16616,13 @@
         <v>22</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>22</v>
+        <v>513</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>22</v>
+        <v>579</v>
       </c>
       <c r="AA113" t="s" s="2">
-        <v>22</v>
+        <v>580</v>
       </c>
       <c r="AB113" t="s" s="2">
         <v>22</v>
@@ -16596,16 +16640,16 @@
         <v>22</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>22</v>
+        <v>581</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>83</v>
@@ -16616,14 +16660,14 @@
         <v>410</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
-        <v>581</v>
+        <v>22</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" t="s" s="2">
@@ -16633,7 +16677,7 @@
         <v>85</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>22</v>
@@ -16642,16 +16686,18 @@
         <v>107</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O114" s="2"/>
-      <c r="P114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="Q114" t="s" s="2">
         <v>22</v>
       </c>
@@ -16699,7 +16745,7 @@
         <v>22</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>76</v>
@@ -16719,18 +16765,18 @@
         <v>410</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
-        <v>586</v>
+        <v>22</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>85</v>
@@ -16745,13 +16791,13 @@
         <v>107</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
@@ -16802,10 +16848,10 @@
         <v>22</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>85</v>
@@ -16822,14 +16868,14 @@
         <v>410</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
-        <v>22</v>
+        <v>592</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" t="s" s="2">
@@ -16839,7 +16885,7 @@
         <v>85</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="J116" t="s" s="2">
         <v>22</v>
@@ -16848,13 +16894,13 @@
         <v>107</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
@@ -16881,13 +16927,13 @@
         <v>22</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>567</v>
+        <v>22</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>594</v>
+        <v>22</v>
       </c>
       <c r="AA116" t="s" s="2">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="AB116" t="s" s="2">
         <v>22</v>
@@ -16905,7 +16951,7 @@
         <v>22</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>76</v>
@@ -16951,13 +16997,13 @@
         <v>107</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>113</v>
+        <v>598</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -17028,14 +17074,14 @@
         <v>410</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
-        <v>601</v>
+        <v>22</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" t="s" s="2">
@@ -17045,7 +17091,7 @@
         <v>85</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="J118" t="s" s="2">
         <v>22</v>
@@ -17062,9 +17108,7 @@
       <c r="N118" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="O118" t="s" s="2">
-        <v>605</v>
-      </c>
+      <c r="O118" s="2"/>
       <c r="P118" s="2"/>
       <c r="Q118" t="s" s="2">
         <v>22</v>
@@ -17089,13 +17133,13 @@
         <v>22</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>22</v>
+        <v>513</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>22</v>
+        <v>605</v>
       </c>
       <c r="AA118" t="s" s="2">
-        <v>22</v>
+        <v>606</v>
       </c>
       <c r="AB118" t="s" s="2">
         <v>22</v>
@@ -17113,7 +17157,7 @@
         <v>22</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>76</v>
@@ -17133,14 +17177,14 @@
         <v>410</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" t="s" s="2">
@@ -17150,7 +17194,7 @@
         <v>85</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="J119" t="s" s="2">
         <v>22</v>
@@ -17159,17 +17203,15 @@
         <v>107</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O119" t="s" s="2">
         <v>610</v>
       </c>
+      <c r="O119" s="2"/>
       <c r="P119" s="2"/>
       <c r="Q119" t="s" s="2">
         <v>22</v>
@@ -17194,13 +17236,13 @@
         <v>22</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>567</v>
+        <v>22</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>611</v>
+        <v>22</v>
       </c>
       <c r="AA119" t="s" s="2">
-        <v>612</v>
+        <v>22</v>
       </c>
       <c r="AB119" t="s" s="2">
         <v>22</v>
@@ -17218,7 +17260,7 @@
         <v>22</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>76</v>
@@ -17238,24 +17280,24 @@
         <v>410</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="J120" t="s" s="2">
         <v>22</v>
@@ -17264,16 +17306,16 @@
         <v>107</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N120" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="P120" s="2"/>
       <c r="Q120" t="s" s="2">
@@ -17323,13 +17365,13 @@
         <v>22</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>22</v>
@@ -17343,21 +17385,21 @@
         <v>410</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
-        <v>22</v>
+        <v>618</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>22</v>
@@ -17372,12 +17414,14 @@
         <v>232</v>
       </c>
       <c r="M121" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="N121" t="s" s="2">
+      <c r="O121" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="O121" s="2"/>
       <c r="P121" s="2"/>
       <c r="Q121" t="s" s="2">
         <v>22</v>
@@ -17402,7 +17446,7 @@
         <v>22</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>567</v>
+        <v>513</v>
       </c>
       <c r="Z121" t="s" s="2">
         <v>622</v>
@@ -17426,13 +17470,13 @@
         <v>22</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>22</v>
@@ -17453,7 +17497,7 @@
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
-        <v>22</v>
+        <v>625</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" t="s" s="2">
@@ -17472,15 +17516,17 @@
         <v>107</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>628</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="P122" s="2"/>
       <c r="Q122" t="s" s="2">
         <v>22</v>
@@ -17549,10 +17595,10 @@
         <v>410</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -17578,14 +17624,12 @@
         <v>232</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>630</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" s="2"/>
       <c r="Q123" t="s" s="2">
         <v>22</v>
@@ -17610,11 +17654,13 @@
         <v>22</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Z123" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="AA123" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AB123" t="s" s="2">
         <v>22</v>
@@ -17632,7 +17678,7 @@
         <v>22</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>76</v>
@@ -17652,10 +17698,10 @@
         <v>410</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -17678,17 +17724,15 @@
         <v>107</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>636</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="O124" s="2"/>
       <c r="P124" s="2"/>
       <c r="Q124" t="s" s="2">
         <v>22</v>
@@ -17737,7 +17781,7 @@
         <v>22</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>76</v>
@@ -17757,10 +17801,10 @@
         <v>410</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -17780,10 +17824,10 @@
         <v>22</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>638</v>
+        <v>232</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>639</v>
@@ -17791,7 +17835,9 @@
       <c r="N125" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="O125" s="2"/>
+      <c r="O125" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="P125" s="2"/>
       <c r="Q125" t="s" s="2">
         <v>22</v>
@@ -17816,13 +17862,11 @@
         <v>22</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="Z125" s="2"/>
       <c r="AA125" t="s" s="2">
-        <v>22</v>
+        <v>642</v>
       </c>
       <c r="AB125" t="s" s="2">
         <v>22</v>
@@ -17840,7 +17884,7 @@
         <v>22</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>76</v>
@@ -17860,14 +17904,14 @@
         <v>410</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
-        <v>642</v>
+        <v>22</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" t="s" s="2">
@@ -17883,19 +17927,19 @@
         <v>22</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P126" s="2"/>
       <c r="Q126" t="s" s="2">
@@ -17945,7 +17989,7 @@
         <v>22</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>76</v>
@@ -17965,10 +18009,10 @@
         <v>410</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -17988,20 +18032,18 @@
         <v>22</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O127" t="s" s="2">
         <v>651</v>
       </c>
+      <c r="O127" s="2"/>
       <c r="P127" s="2"/>
       <c r="Q127" t="s" s="2">
         <v>22</v>
@@ -18050,7 +18092,7 @@
         <v>22</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>76</v>
@@ -18093,23 +18135,21 @@
         <v>22</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>232</v>
+        <v>654</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="P128" t="s" s="2">
         <v>657</v>
       </c>
+      <c r="P128" s="2"/>
       <c r="Q128" t="s" s="2">
         <v>22</v>
       </c>
@@ -18133,13 +18173,13 @@
         <v>22</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>567</v>
+        <v>22</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>658</v>
+        <v>22</v>
       </c>
       <c r="AA128" t="s" s="2">
-        <v>659</v>
+        <v>22</v>
       </c>
       <c r="AB128" t="s" s="2">
         <v>22</v>
@@ -18177,10 +18217,10 @@
         <v>410</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -18200,18 +18240,20 @@
         <v>22</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="M129" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="O129" s="2"/>
       <c r="P129" s="2"/>
       <c r="Q129" t="s" s="2">
         <v>22</v>
@@ -18260,7 +18302,7 @@
         <v>22</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>76</v>
@@ -18287,14 +18329,14 @@
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
-        <v>22</v>
+        <v>664</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>22</v>
@@ -18306,16 +18348,20 @@
         <v>107</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>86</v>
+        <v>232</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O130" s="2"/>
-      <c r="P130" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="Q130" t="s" s="2">
         <v>22</v>
       </c>
@@ -18339,13 +18385,13 @@
         <v>22</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>22</v>
+        <v>513</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>22</v>
+        <v>669</v>
       </c>
       <c r="AA130" t="s" s="2">
-        <v>22</v>
+        <v>670</v>
       </c>
       <c r="AB130" t="s" s="2">
         <v>22</v>
@@ -18369,7 +18415,7 @@
         <v>76</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>22</v>
@@ -18383,10 +18429,10 @@
         <v>410</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -18409,17 +18455,15 @@
         <v>22</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>668</v>
+        <v>53</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>670</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" s="2"/>
       <c r="Q131" t="s" s="2">
         <v>22</v>
@@ -18468,7 +18512,7 @@
         <v>22</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>76</v>
@@ -18485,13 +18529,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>671</v>
+        <v>410</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>242</v>
+        <v>674</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>242</v>
+        <v>674</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -18502,7 +18546,7 @@
         <v>76</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>22</v>
@@ -18511,20 +18555,18 @@
         <v>22</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
         <v>22</v>
@@ -18573,30 +18615,30 @@
         <v>22</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>242</v>
+        <v>674</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>679</v>
+        <v>83</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>671</v>
+        <v>410</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>248</v>
+        <v>677</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>248</v>
+        <v>677</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -18607,7 +18649,7 @@
         <v>76</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>22</v>
@@ -18619,15 +18661,17 @@
         <v>22</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>86</v>
+        <v>678</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>87</v>
+        <v>679</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>680</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>681</v>
+      </c>
       <c r="P133" s="2"/>
       <c r="Q133" t="s" s="2">
         <v>22</v>
@@ -18676,34 +18720,34 @@
         <v>22</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>89</v>
+        <v>677</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" t="s" s="2">
@@ -18722,16 +18766,16 @@
         <v>22</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>93</v>
+        <v>688</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>94</v>
+        <v>689</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="P134" s="2"/>
       <c r="Q134" t="s" s="2">
@@ -18769,19 +18813,19 @@
         <v>22</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AD134" t="s" s="2">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="AE134" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>99</v>
+        <v>242</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>76</v>
@@ -18790,25 +18834,23 @@
         <v>77</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>100</v>
+        <v>690</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="D135" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
         <v>22</v>
       </c>
@@ -18829,13 +18871,13 @@
         <v>22</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>252</v>
+        <v>86</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>253</v>
+        <v>87</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>680</v>
+        <v>88</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
@@ -18886,41 +18928,41 @@
         <v>22</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>22</v>
@@ -18929,23 +18971,21 @@
         <v>22</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>256</v>
+        <v>92</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>257</v>
+        <v>93</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>258</v>
+        <v>94</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P136" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="P136" s="2"/>
       <c r="Q136" t="s" s="2">
         <v>22</v>
       </c>
@@ -18981,44 +19021,46 @@
         <v>22</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="AD136" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AE136" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>255</v>
+        <v>99</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D137" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="D137" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="E137" t="s" s="2">
         <v>22</v>
       </c>
@@ -19039,13 +19081,13 @@
         <v>22</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>86</v>
+        <v>252</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>263</v>
+        <v>691</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
@@ -19096,30 +19138,30 @@
         <v>22</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -19130,7 +19172,7 @@
         <v>76</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>22</v>
@@ -19139,19 +19181,23 @@
         <v>22</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>92</v>
+        <v>256</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>126</v>
+        <v>257</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O138" s="2"/>
-      <c r="P138" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="Q138" t="s" s="2">
         <v>22</v>
       </c>
@@ -19187,44 +19233,44 @@
         <v>22</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AD138" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="AE138" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>99</v>
+        <v>255</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="D139" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
         <v>22</v>
       </c>
@@ -19245,17 +19291,15 @@
         <v>22</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>267</v>
+        <v>86</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" s="2"/>
       <c r="Q139" t="s" s="2">
         <v>22</v>
@@ -19304,34 +19348,32 @@
         <v>22</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C140" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="D140" t="s" s="2">
-        <v>272</v>
-      </c>
+      <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
         <v>22</v>
       </c>
@@ -19340,7 +19382,7 @@
         <v>76</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>22</v>
@@ -19352,13 +19394,13 @@
         <v>22</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>273</v>
+        <v>92</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>274</v>
+        <v>126</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>314</v>
+        <v>132</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
@@ -19397,16 +19439,14 @@
         <v>22</v>
       </c>
       <c r="AC140" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AD140" s="2"/>
       <c r="AE140" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>99</v>
@@ -19418,7 +19458,7 @@
         <v>77</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>100</v>
@@ -19426,15 +19466,17 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="D141" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="D141" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="E141" t="s" s="2">
         <v>22</v>
       </c>
@@ -19455,15 +19497,17 @@
         <v>22</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O141" s="2"/>
+        <v>692</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P141" s="2"/>
       <c r="Q141" t="s" s="2">
         <v>22</v>
@@ -19512,32 +19556,34 @@
         <v>22</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>279</v>
+        <v>99</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="D142" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="D142" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="E142" t="s" s="2">
         <v>22</v>
       </c>
@@ -19546,36 +19592,32 @@
         <v>76</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>22</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>168</v>
+        <v>273</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>682</v>
+        <v>314</v>
       </c>
       <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="P142" s="2"/>
       <c r="Q142" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="R142" t="s" s="2">
-        <v>284</v>
-      </c>
+      <c r="R142" s="2"/>
       <c r="S142" t="s" s="2">
         <v>22</v>
       </c>
@@ -19595,13 +19637,13 @@
         <v>22</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>173</v>
+        <v>22</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>285</v>
+        <v>22</v>
       </c>
       <c r="AA142" t="s" s="2">
-        <v>286</v>
+        <v>22</v>
       </c>
       <c r="AB142" t="s" s="2">
         <v>22</v>
@@ -19619,30 +19661,30 @@
         <v>22</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>280</v>
+        <v>99</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -19662,21 +19704,19 @@
         <v>22</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="O143" s="2"/>
-      <c r="P143" t="s" s="2">
-        <v>290</v>
-      </c>
+      <c r="P143" s="2"/>
       <c r="Q143" t="s" s="2">
         <v>22</v>
       </c>
@@ -19724,7 +19764,7 @@
         <v>22</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>76</v>
@@ -19736,18 +19776,18 @@
         <v>22</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -19758,34 +19798,36 @@
         <v>76</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>22</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="K144" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>293</v>
+        <v>693</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="Q144" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="R144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="S144" t="s" s="2">
         <v>22</v>
       </c>
@@ -19805,13 +19847,13 @@
         <v>22</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>22</v>
+        <v>173</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>22</v>
+        <v>285</v>
       </c>
       <c r="AA144" t="s" s="2">
-        <v>22</v>
+        <v>286</v>
       </c>
       <c r="AB144" t="s" s="2">
         <v>22</v>
@@ -19829,7 +19871,7 @@
         <v>22</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>76</v>
@@ -19838,7 +19880,7 @@
         <v>85</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>295</v>
+        <v>22</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>83</v>
@@ -19846,13 +19888,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -19875,19 +19917,17 @@
         <v>107</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="Q145" t="s" s="2">
         <v>22</v>
@@ -19936,7 +19976,7 @@
         <v>22</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>76</v>
@@ -19948,6 +19988,218 @@
         <v>22</v>
       </c>
       <c r="AK145" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="D146" s="2"/>
+      <c r="E146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F146" s="2"/>
+      <c r="G146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Q146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R146" s="2"/>
+      <c r="S146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="D147" s="2"/>
+      <c r="E147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F147" s="2"/>
+      <c r="G147" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="P147" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Q147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R147" s="2"/>
+      <c r="S147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK147" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T10:04:42+05:30</t>
+    <t>2026-05-16T10:41:11+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:58:39+05:30</t>
+    <t>2026-05-16T13:10:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -816,9 +816,9 @@
 workflow, and source-system-native semantic classifications and source system fidelity.
 Any coding system intended to represent an internal coding
 system SHALL follow the required naming convention:
-[customer]-[ehr]-[ResourceType]-[resource-subtype]-[element]-[source-specific-string]-InternalCode
+[customer]-[ehr]-[ResourceType]-[resource-subtype]-[element]-[SourceSpecificString]-InternalCode
 Example:
-acme-epic-Observation-lab-code-glucose-InternalCode</t>
+acme-epic-Observation-lab-code-Glucose-InternalCode</t>
   </si>
   <si>
     <t>CodeableConcept</t>
@@ -915,9 +915,6 @@
   </si>
   <si>
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>acme-epic-Observation-lab-code-Glucose-InternalCode</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1043,7 +1040,17 @@
 Display: "Blood Culture"
 Generated code: "blood-culture"
 Whenever either code or display is populated, system SHALL
-also be populated.</t>
+also be populated.
+This data type supports:
+- standard terminology codings
+- optional customer-specific internal codings
+Internal codings are used to preserve customer, EHR,
+workflow, and source-system-native semantic classifications and source system fidelity.
+Any coding system intended to represent an internal coding
+system SHALL follow the required naming convention:
+[customer]-[ehr]-[ResourceType]-[resource-subtype]-[element]-[SourceSpecificString]-InternalCode
+Example:
+acme-epic-Observation-lab-code-Glucose-InternalCode</t>
   </si>
   <si>
     <t>Coding</t>
@@ -1079,9 +1086,12 @@
 workflow, and source-system-native semantic classifications and source system fidelity.
 Any coding system intended to represent an internal coding
 system SHALL follow the required naming convention:
-[customer]-[ehr]-[ResourceType]-[resource-subtype]-[element]-[source-specific-string]-InternalCode
+[customer]-[ehr]-[ResourceType]-[resource-subtype]-[element]-[SourceSpecificString]-InternalCode
 Example:
-acme-epic-Observation-lab-code-glucose-InternalCode</t>
+acme-epic-Observation-lab-code-Glucose-InternalCode</t>
+  </si>
+  <si>
+    <t>acme-epic-Observation-lab-code-Glucose-InternalCode</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1146,7 +1156,7 @@
 Identifier.system SHALL follow the naming convention:
 [customer]-[ehr]-[ResourceType]-[resource-subtype]-[eleMent]-[SourceSpecificString]-InternalIdentifier
 Example:
-acme-epic-Patient--identifier-MRN-InternalIdentifier</t>
+acme-cerner-Observation-lab-identifier-AccessionNumber-InternalIdentifier</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -3924,7 +3934,7 @@
         <v>2</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="132">
@@ -3932,7 +3942,7 @@
         <v>4</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="133">
@@ -3948,7 +3958,7 @@
         <v>8</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="135">
@@ -3956,7 +3966,7 @@
         <v>10</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="136">
@@ -4010,7 +4020,7 @@
         <v>23</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="143">
@@ -4046,7 +4056,7 @@
         <v>32</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="148">
@@ -4054,7 +4064,7 @@
         <v>34</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="149">
@@ -10331,43 +10341,43 @@
         <v>22</v>
       </c>
       <c r="U44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG44" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>76</v>
@@ -10387,10 +10397,10 @@
         <v>237</v>
       </c>
       <c r="B45" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -10416,13 +10426,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
@@ -10472,7 +10482,7 @@
         <v>22</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>76</v>
@@ -10492,10 +10502,10 @@
         <v>237</v>
       </c>
       <c r="B46" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -10521,14 +10531,14 @@
         <v>168</v>
       </c>
       <c r="M46" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q46" t="s" s="2">
         <v>22</v>
@@ -10577,7 +10587,7 @@
         <v>22</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
@@ -10597,10 +10607,10 @@
         <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -10626,14 +10636,14 @@
         <v>86</v>
       </c>
       <c r="M47" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>22</v>
@@ -10682,7 +10692,7 @@
         <v>22</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -10702,10 +10712,10 @@
         <v>237</v>
       </c>
       <c r="B48" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -10728,19 +10738,19 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="O48" t="s" s="2">
+      <c r="P48" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="Q48" t="s" s="2">
         <v>22</v>
@@ -10789,7 +10799,7 @@
         <v>22</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -10809,10 +10819,10 @@
         <v>237</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -10838,16 +10848,16 @@
         <v>86</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="O49" t="s" s="2">
+      <c r="P49" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="Q49" t="s" s="2">
         <v>22</v>
@@ -10896,7 +10906,7 @@
         <v>22</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
@@ -10913,13 +10923,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -10945,13 +10955,13 @@
         <v>78</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>253</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
@@ -11001,7 +11011,7 @@
         <v>22</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>76</v>
@@ -11013,18 +11023,18 @@
         <v>82</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -11121,13 +11131,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -11226,13 +11236,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -11258,10 +11268,10 @@
         <v>134</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>270</v>
@@ -11280,43 +11290,43 @@
         <v>22</v>
       </c>
       <c r="U53" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG53" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>76</v>
@@ -11333,13 +11343,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -11371,7 +11381,7 @@
         <v>321</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -11421,7 +11431,7 @@
         <v>22</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>76</v>
@@ -11438,13 +11448,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -11477,7 +11487,7 @@
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q55" t="s" s="2">
         <v>22</v>
@@ -11526,7 +11536,7 @@
         <v>22</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
@@ -11543,13 +11553,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -11582,7 +11592,7 @@
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>22</v>
@@ -11631,7 +11641,7 @@
         <v>22</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>76</v>
@@ -11648,13 +11658,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -11677,19 +11687,19 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>326</v>
       </c>
       <c r="O57" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="P57" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="Q57" t="s" s="2">
         <v>22</v>
@@ -11738,7 +11748,7 @@
         <v>22</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
@@ -19944,7 +19954,7 @@
         <v>107</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M136" t="s" s="2">
         <v>676</v>
@@ -20581,16 +20591,16 @@
         <v>86</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>698</v>
       </c>
       <c r="O142" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="P142" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="P142" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="Q142" t="s" s="2">
         <v>22</v>
@@ -20639,7 +20649,7 @@
         <v>22</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>76</v>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/all-profiles.xlsx
+++ b/314e-ig/output/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23577" uniqueCount="1542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23577" uniqueCount="1544">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3187,6 +3187,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/observation-lab-general-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
+</t>
+  </si>
+  <si>
     <t>observation-microbiology-314e</t>
   </si>
   <si>
@@ -3257,6 +3261,10 @@
   </si>
   <si>
     <t>antimicrobialSusceptibilityObservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
+</t>
   </si>
   <si>
     <t>period-314e</t>
@@ -8020,7 +8028,7 @@
         <v>2</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="344">
@@ -8044,7 +8052,7 @@
         <v>8</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="347">
@@ -8052,7 +8060,7 @@
         <v>10</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="348">
@@ -8106,7 +8114,7 @@
         <v>23</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="355">
@@ -8182,7 +8190,7 @@
         <v>2</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="365">
@@ -8190,7 +8198,7 @@
         <v>4</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="366">
@@ -8206,7 +8214,7 @@
         <v>8</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="368">
@@ -8214,7 +8222,7 @@
         <v>10</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="369">
@@ -8268,7 +8276,7 @@
         <v>23</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="376">
@@ -8344,7 +8352,7 @@
         <v>2</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="386">
@@ -8352,7 +8360,7 @@
         <v>4</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="387">
@@ -8368,7 +8376,7 @@
         <v>8</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="389">
@@ -8376,7 +8384,7 @@
         <v>10</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="390">
@@ -8430,7 +8438,7 @@
         <v>23</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="397">
@@ -8466,7 +8474,7 @@
         <v>32</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="402">
@@ -8474,7 +8482,7 @@
         <v>34</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="403">
@@ -8506,7 +8514,7 @@
         <v>2</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="407">
@@ -8514,7 +8522,7 @@
         <v>4</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="408">
@@ -8530,7 +8538,7 @@
         <v>8</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="410">
@@ -8538,7 +8546,7 @@
         <v>10</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="411">
@@ -8592,7 +8600,7 @@
         <v>23</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="418">
@@ -8628,7 +8636,7 @@
         <v>32</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
     </row>
     <row r="423">
@@ -8636,7 +8644,7 @@
         <v>34</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="424">
@@ -8668,7 +8676,7 @@
         <v>2</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="428">
@@ -8676,7 +8684,7 @@
         <v>4</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="429">
@@ -8692,7 +8700,7 @@
         <v>8</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="431">
@@ -8700,7 +8708,7 @@
         <v>10</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="432">
@@ -8754,7 +8762,7 @@
         <v>23</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="439">
@@ -8762,7 +8770,7 @@
         <v>25</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="440">
@@ -8824,7 +8832,7 @@
         <v>132</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="448">
@@ -8840,7 +8848,7 @@
         <v>2</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="450">
@@ -8848,7 +8856,7 @@
         <v>4</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="451">
@@ -8864,7 +8872,7 @@
         <v>8</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="453">
@@ -8872,7 +8880,7 @@
         <v>10</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1023</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="454">
@@ -8926,7 +8934,7 @@
         <v>23</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="461">
@@ -8934,7 +8942,7 @@
         <v>25</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="462">
@@ -8996,7 +9004,7 @@
         <v>132</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="470">
@@ -9012,7 +9020,7 @@
         <v>2</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="472">
@@ -9020,7 +9028,7 @@
         <v>4</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="473">
@@ -9036,7 +9044,7 @@
         <v>8</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1031</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="475">
@@ -9044,7 +9052,7 @@
         <v>10</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="476">
@@ -9098,7 +9106,7 @@
         <v>23</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="483">
@@ -9134,7 +9142,7 @@
         <v>32</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="488">
@@ -9142,7 +9150,7 @@
         <v>34</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1035</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="489">
@@ -9174,7 +9182,7 @@
         <v>2</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="493">
@@ -9182,7 +9190,7 @@
         <v>4</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="494">
@@ -9198,7 +9206,7 @@
         <v>8</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="496">
@@ -9206,7 +9214,7 @@
         <v>10</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="497">
@@ -9260,7 +9268,7 @@
         <v>23</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="504">
@@ -9296,7 +9304,7 @@
         <v>32</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="509">
@@ -9304,7 +9312,7 @@
         <v>34</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="510">
@@ -9336,7 +9344,7 @@
         <v>2</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="514">
@@ -9344,7 +9352,7 @@
         <v>4</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="515">
@@ -9360,7 +9368,7 @@
         <v>8</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1072</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="517">
@@ -9368,7 +9376,7 @@
         <v>10</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="518">
@@ -9422,7 +9430,7 @@
         <v>23</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="525">
@@ -9430,7 +9438,7 @@
         <v>25</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="526">
@@ -9460,7 +9468,7 @@
         <v>32</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="530">
@@ -9468,7 +9476,7 @@
         <v>34</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1077</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="531">
@@ -9500,7 +9508,7 @@
         <v>2</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="535">
@@ -9508,7 +9516,7 @@
         <v>4</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="536">
@@ -9524,7 +9532,7 @@
         <v>8</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="538">
@@ -9532,7 +9540,7 @@
         <v>10</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="539">
@@ -9586,7 +9594,7 @@
         <v>23</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="546">
@@ -9594,7 +9602,7 @@
         <v>25</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1113</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="547">
@@ -9656,7 +9664,7 @@
         <v>132</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="555">
@@ -9672,7 +9680,7 @@
         <v>2</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="557">
@@ -9680,7 +9688,7 @@
         <v>4</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="558">
@@ -9696,7 +9704,7 @@
         <v>8</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="560">
@@ -9704,7 +9712,7 @@
         <v>10</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1121</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="561">
@@ -9758,7 +9766,7 @@
         <v>23</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="568">
@@ -9794,7 +9802,7 @@
         <v>32</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="573">
@@ -9802,7 +9810,7 @@
         <v>34</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="574">
@@ -9834,7 +9842,7 @@
         <v>2</v>
       </c>
       <c r="B577" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="578">
@@ -9842,7 +9850,7 @@
         <v>4</v>
       </c>
       <c r="B578" t="s" s="2">
-        <v>1157</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="579">
@@ -9858,7 +9866,7 @@
         <v>8</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="581">
@@ -9866,7 +9874,7 @@
         <v>10</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>1159</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="582">
@@ -9920,7 +9928,7 @@
         <v>23</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>1160</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="589">
@@ -9928,7 +9936,7 @@
         <v>25</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>1161</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="590">
@@ -9958,7 +9966,7 @@
         <v>32</v>
       </c>
       <c r="B593" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="594">
@@ -9966,7 +9974,7 @@
         <v>34</v>
       </c>
       <c r="B594" t="s" s="2">
-        <v>1163</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="595">
@@ -9998,7 +10006,7 @@
         <v>2</v>
       </c>
       <c r="B598" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="599">
@@ -10006,7 +10014,7 @@
         <v>4</v>
       </c>
       <c r="B599" t="s" s="2">
-        <v>1393</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="600">
@@ -10022,7 +10030,7 @@
         <v>8</v>
       </c>
       <c r="B601" t="s" s="2">
-        <v>1394</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="602">
@@ -10030,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="B602" t="s" s="2">
-        <v>1395</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="603">
@@ -10084,7 +10092,7 @@
         <v>23</v>
       </c>
       <c r="B609" t="s" s="2">
-        <v>1396</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="610">
@@ -10120,7 +10128,7 @@
         <v>32</v>
       </c>
       <c r="B614" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
     </row>
     <row r="615">
@@ -10128,7 +10136,7 @@
         <v>34</v>
       </c>
       <c r="B615" t="s" s="2">
-        <v>1397</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="616">
@@ -10160,7 +10168,7 @@
         <v>2</v>
       </c>
       <c r="B619" t="s" s="2">
-        <v>1406</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="620">
@@ -10168,7 +10176,7 @@
         <v>4</v>
       </c>
       <c r="B620" t="s" s="2">
-        <v>1407</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="621">
@@ -10184,7 +10192,7 @@
         <v>8</v>
       </c>
       <c r="B622" t="s" s="2">
-        <v>1408</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="623">
@@ -10192,7 +10200,7 @@
         <v>10</v>
       </c>
       <c r="B623" t="s" s="2">
-        <v>1409</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="624">
@@ -10246,7 +10254,7 @@
         <v>23</v>
       </c>
       <c r="B630" t="s" s="2">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="631">
@@ -10282,7 +10290,7 @@
         <v>32</v>
       </c>
       <c r="B635" t="s" s="2">
-        <v>1411</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="636">
@@ -10290,7 +10298,7 @@
         <v>34</v>
       </c>
       <c r="B636" t="s" s="2">
-        <v>1412</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="637">
@@ -10322,7 +10330,7 @@
         <v>2</v>
       </c>
       <c r="B640" t="s" s="2">
-        <v>1427</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="641">
@@ -10330,7 +10338,7 @@
         <v>4</v>
       </c>
       <c r="B641" t="s" s="2">
-        <v>1428</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="642">
@@ -10346,7 +10354,7 @@
         <v>8</v>
       </c>
       <c r="B643" t="s" s="2">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="644">
@@ -10354,7 +10362,7 @@
         <v>10</v>
       </c>
       <c r="B644" t="s" s="2">
-        <v>1430</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="645">
@@ -10410,7 +10418,7 @@
         <v>23</v>
       </c>
       <c r="B651" t="s" s="2">
-        <v>1431</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="652">
@@ -10478,7 +10486,7 @@
         <v>132</v>
       </c>
       <c r="B660" t="s" s="2">
-        <v>1432</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="661">
@@ -10494,7 +10502,7 @@
         <v>2</v>
       </c>
       <c r="B662" t="s" s="2">
-        <v>1435</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="663">
@@ -10502,7 +10510,7 @@
         <v>4</v>
       </c>
       <c r="B663" t="s" s="2">
-        <v>1436</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="664">
@@ -10518,7 +10526,7 @@
         <v>8</v>
       </c>
       <c r="B665" t="s" s="2">
-        <v>1437</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="666">
@@ -10526,7 +10534,7 @@
         <v>10</v>
       </c>
       <c r="B666" t="s" s="2">
-        <v>1438</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="667">
@@ -10582,7 +10590,7 @@
         <v>23</v>
       </c>
       <c r="B673" t="s" s="2">
-        <v>1439</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="674">
@@ -10650,7 +10658,7 @@
         <v>132</v>
       </c>
       <c r="B682" t="s" s="2">
-        <v>1432</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="683">
@@ -10666,7 +10674,7 @@
         <v>2</v>
       </c>
       <c r="B684" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="685">
@@ -10674,7 +10682,7 @@
         <v>4</v>
       </c>
       <c r="B685" t="s" s="2">
-        <v>1445</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="686">
@@ -10690,7 +10698,7 @@
         <v>8</v>
       </c>
       <c r="B687" t="s" s="2">
-        <v>1446</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="688">
@@ -10698,7 +10706,7 @@
         <v>10</v>
       </c>
       <c r="B688" t="s" s="2">
-        <v>1447</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="689">
@@ -10752,7 +10760,7 @@
         <v>23</v>
       </c>
       <c r="B695" t="s" s="2">
-        <v>1448</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="696">
@@ -10788,7 +10796,7 @@
         <v>32</v>
       </c>
       <c r="B700" t="s" s="2">
-        <v>1449</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="701">
@@ -10796,7 +10804,7 @@
         <v>34</v>
       </c>
       <c r="B701" t="s" s="2">
-        <v>1450</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="702">
@@ -10828,7 +10836,7 @@
         <v>2</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1534</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="706">
@@ -10836,7 +10844,7 @@
         <v>4</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="707">
@@ -10852,7 +10860,7 @@
         <v>8</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="709">
@@ -10860,7 +10868,7 @@
         <v>10</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="710">
@@ -10914,7 +10922,7 @@
         <v>23</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1538</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="717">
@@ -10982,7 +10990,7 @@
         <v>132</v>
       </c>
       <c r="B725" t="s" s="2">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
   </sheetData>
@@ -40376,7 +40384,7 @@
         <v>107</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>881</v>
@@ -42457,7 +42465,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>526</v>
@@ -42562,7 +42570,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>533</v>
@@ -42667,7 +42675,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>539</v>
@@ -42770,7 +42778,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>544</v>
@@ -42873,7 +42881,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>545</v>
@@ -42978,7 +42986,7 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>546</v>
@@ -43083,7 +43091,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>551</v>
@@ -43188,7 +43196,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>556</v>
@@ -43293,7 +43301,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>561</v>
@@ -43398,7 +43406,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>567</v>
@@ -43503,7 +43511,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>575</v>
@@ -43608,7 +43616,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>583</v>
@@ -43713,7 +43721,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>588</v>
@@ -43818,7 +43826,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>594</v>
@@ -43923,7 +43931,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>601</v>
@@ -44028,7 +44036,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>608</v>
@@ -44129,7 +44137,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>610</v>
@@ -44234,7 +44242,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>615</v>
@@ -44341,7 +44349,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>620</v>
@@ -44444,7 +44452,7 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>626</v>
@@ -44551,7 +44559,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>630</v>
@@ -44654,7 +44662,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>632</v>
@@ -44759,7 +44767,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>634</v>
@@ -44866,7 +44874,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>636</v>
@@ -44973,7 +44981,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>638</v>
@@ -45080,7 +45088,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>640</v>
@@ -45185,7 +45193,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>642</v>
@@ -45288,7 +45296,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>644</v>
@@ -45393,7 +45401,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>646</v>
@@ -45498,7 +45506,7 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>652</v>
@@ -45603,7 +45611,7 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>658</v>
@@ -45710,7 +45718,7 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>665</v>
@@ -45815,7 +45823,7 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>673</v>
@@ -45924,7 +45932,7 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>678</v>
@@ -46031,7 +46039,7 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>684</v>
@@ -46138,7 +46146,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>723</v>
@@ -46245,7 +46253,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>729</v>
@@ -46350,7 +46358,7 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>734</v>
@@ -46457,7 +46465,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>741</v>
@@ -46564,7 +46572,7 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>750</v>
@@ -46669,7 +46677,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>755</v>
@@ -46774,7 +46782,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>760</v>
@@ -46881,7 +46889,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>768</v>
@@ -46988,7 +46996,7 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>777</v>
@@ -47095,7 +47103,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>785</v>
@@ -47202,7 +47210,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>791</v>
@@ -47307,7 +47315,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B346" t="s" s="2">
         <v>797</v>
@@ -47414,7 +47422,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B347" t="s" s="2">
         <v>824</v>
@@ -47519,7 +47527,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>829</v>
@@ -47624,7 +47632,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B349" t="s" s="2">
         <v>834</v>
@@ -47731,7 +47739,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B350" t="s" s="2">
         <v>842</v>
@@ -47834,7 +47842,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B351" t="s" s="2">
         <v>843</v>
@@ -47939,7 +47947,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B352" t="s" s="2">
         <v>844</v>
@@ -48046,7 +48054,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B353" t="s" s="2">
         <v>849</v>
@@ -48149,7 +48157,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>854</v>
@@ -48252,7 +48260,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B355" t="s" s="2">
         <v>857</v>
@@ -48359,7 +48367,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B356" t="s" s="2">
         <v>864</v>
@@ -48466,7 +48474,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B357" t="s" s="2">
         <v>871</v>
@@ -48571,7 +48579,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B358" t="s" s="2">
         <v>876</v>
@@ -48674,7 +48682,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B359" t="s" s="2">
         <v>879</v>
@@ -48777,7 +48785,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B360" t="s" s="2">
         <v>885</v>
@@ -48884,7 +48892,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B361" t="s" s="2">
         <v>887</v>
@@ -48989,7 +48997,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B362" t="s" s="2">
         <v>892</v>
@@ -49096,7 +49104,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B363" t="s" s="2">
         <v>897</v>
@@ -49199,7 +49207,7 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B364" t="s" s="2">
         <v>898</v>
@@ -49304,7 +49312,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B365" t="s" s="2">
         <v>899</v>
@@ -49411,7 +49419,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B366" t="s" s="2">
         <v>900</v>
@@ -49518,7 +49526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B367" t="s" s="2">
         <v>906</v>
@@ -49625,7 +49633,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B368" t="s" s="2">
         <v>910</v>
@@ -49732,7 +49740,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B369" t="s" s="2">
         <v>915</v>
@@ -49839,7 +49847,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B370" t="s" s="2">
         <v>917</v>
@@ -49946,7 +49954,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B371" t="s" s="2">
         <v>921</v>
@@ -50049,7 +50057,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B372" t="s" s="2">
         <v>922</v>
@@ -50154,7 +50162,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B373" t="s" s="2">
         <v>923</v>
@@ -50261,7 +50269,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B374" t="s" s="2">
         <v>924</v>
@@ -50364,7 +50372,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B375" t="s" s="2">
         <v>925</v>
@@ -50467,7 +50475,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B376" t="s" s="2">
         <v>926</v>
@@ -50574,7 +50582,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B377" t="s" s="2">
         <v>928</v>
@@ -50681,7 +50689,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B378" t="s" s="2">
         <v>930</v>
@@ -50786,7 +50794,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B379" t="s" s="2">
         <v>931</v>
@@ -50889,7 +50897,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B380" t="s" s="2">
         <v>526</v>
@@ -50994,7 +51002,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B381" t="s" s="2">
         <v>533</v>
@@ -51099,7 +51107,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B382" t="s" s="2">
         <v>539</v>
@@ -51202,7 +51210,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B383" t="s" s="2">
         <v>544</v>
@@ -51305,7 +51313,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B384" t="s" s="2">
         <v>545</v>
@@ -51410,7 +51418,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>546</v>
@@ -51515,7 +51523,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B386" t="s" s="2">
         <v>551</v>
@@ -51620,7 +51628,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B387" t="s" s="2">
         <v>556</v>
@@ -51725,7 +51733,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B388" t="s" s="2">
         <v>561</v>
@@ -51830,7 +51838,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B389" t="s" s="2">
         <v>567</v>
@@ -51935,7 +51943,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>575</v>
@@ -52040,7 +52048,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>583</v>
@@ -52145,7 +52153,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>588</v>
@@ -52250,7 +52258,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>594</v>
@@ -52355,7 +52363,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>601</v>
@@ -52460,7 +52468,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>608</v>
@@ -52561,7 +52569,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>610</v>
@@ -52666,7 +52674,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>615</v>
@@ -52773,7 +52781,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>620</v>
@@ -52876,7 +52884,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>626</v>
@@ -52983,7 +52991,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>630</v>
@@ -53086,7 +53094,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>632</v>
@@ -53191,7 +53199,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>634</v>
@@ -53298,7 +53306,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>636</v>
@@ -53405,7 +53413,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>638</v>
@@ -53512,7 +53520,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>640</v>
@@ -53617,7 +53625,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>642</v>
@@ -53720,7 +53728,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>644</v>
@@ -53825,7 +53833,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>646</v>
@@ -53930,7 +53938,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>652</v>
@@ -54035,7 +54043,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>658</v>
@@ -54142,7 +54150,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>665</v>
@@ -54247,7 +54255,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>673</v>
@@ -54356,7 +54364,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B413" t="s" s="2">
         <v>678</v>
@@ -54463,7 +54471,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B414" t="s" s="2">
         <v>684</v>
@@ -54570,7 +54578,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B415" t="s" s="2">
         <v>692</v>
@@ -54673,7 +54681,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B416" t="s" s="2">
         <v>693</v>
@@ -54778,7 +54786,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B417" t="s" s="2">
         <v>694</v>
@@ -54883,7 +54891,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B418" t="s" s="2">
         <v>695</v>
@@ -54992,7 +55000,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B419" t="s" s="2">
         <v>696</v>
@@ -55095,7 +55103,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B420" t="s" s="2">
         <v>698</v>
@@ -55200,7 +55208,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B421" t="s" s="2">
         <v>700</v>
@@ -55307,7 +55315,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B422" t="s" s="2">
         <v>702</v>
@@ -55412,7 +55420,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B423" t="s" s="2">
         <v>704</v>
@@ -55517,7 +55525,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B424" t="s" s="2">
         <v>706</v>
@@ -55622,7 +55630,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B425" t="s" s="2">
         <v>708</v>
@@ -55729,16 +55737,16 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C426" t="s" s="2">
         <v>694</v>
       </c>
       <c r="D426" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="E426" t="s" s="2">
         <v>22</v>
@@ -55838,10 +55846,10 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C427" t="s" s="2">
         <v>697</v>
@@ -55941,10 +55949,10 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C428" t="s" s="2">
         <v>699</v>
@@ -56046,10 +56054,10 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C429" t="s" s="2">
         <v>701</v>
@@ -56094,7 +56102,7 @@
       </c>
       <c r="R429" s="2"/>
       <c r="S429" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="T429" t="s" s="2">
         <v>22</v>
@@ -56153,10 +56161,10 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C430" t="s" s="2">
         <v>703</v>
@@ -56258,10 +56266,10 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C431" t="s" s="2">
         <v>705</v>
@@ -56304,7 +56312,7 @@
       </c>
       <c r="R431" s="2"/>
       <c r="S431" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="T431" t="s" s="2">
         <v>22</v>
@@ -56363,10 +56371,10 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C432" t="s" s="2">
         <v>707</v>
@@ -56409,7 +56417,7 @@
       </c>
       <c r="R432" s="2"/>
       <c r="S432" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="T432" t="s" s="2">
         <v>22</v>
@@ -56468,10 +56476,10 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C433" t="s" s="2">
         <v>709</v>
@@ -56575,7 +56583,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B434" t="s" s="2">
         <v>722</v>
@@ -56682,7 +56690,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B435" t="s" s="2">
         <v>723</v>
@@ -56789,7 +56797,7 @@
     </row>
     <row r="436">
       <c r="A436" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B436" t="s" s="2">
         <v>729</v>
@@ -56894,7 +56902,7 @@
     </row>
     <row r="437">
       <c r="A437" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B437" t="s" s="2">
         <v>734</v>
@@ -57001,7 +57009,7 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B438" t="s" s="2">
         <v>741</v>
@@ -57108,7 +57116,7 @@
     </row>
     <row r="439">
       <c r="A439" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B439" t="s" s="2">
         <v>750</v>
@@ -57213,7 +57221,7 @@
     </row>
     <row r="440">
       <c r="A440" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B440" t="s" s="2">
         <v>755</v>
@@ -57318,7 +57326,7 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B441" t="s" s="2">
         <v>760</v>
@@ -57425,7 +57433,7 @@
     </row>
     <row r="442">
       <c r="A442" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B442" t="s" s="2">
         <v>768</v>
@@ -57532,7 +57540,7 @@
     </row>
     <row r="443">
       <c r="A443" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B443" t="s" s="2">
         <v>777</v>
@@ -57639,7 +57647,7 @@
     </row>
     <row r="444">
       <c r="A444" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B444" t="s" s="2">
         <v>785</v>
@@ -57746,7 +57754,7 @@
     </row>
     <row r="445">
       <c r="A445" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B445" t="s" s="2">
         <v>791</v>
@@ -57851,7 +57859,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B446" t="s" s="2">
         <v>797</v>
@@ -57958,7 +57966,7 @@
     </row>
     <row r="447">
       <c r="A447" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B447" t="s" s="2">
         <v>804</v>
@@ -58061,7 +58069,7 @@
     </row>
     <row r="448">
       <c r="A448" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B448" t="s" s="2">
         <v>805</v>
@@ -58166,7 +58174,7 @@
     </row>
     <row r="449">
       <c r="A449" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B449" t="s" s="2">
         <v>806</v>
@@ -58236,7 +58244,7 @@
       </c>
       <c r="Z449" s="2"/>
       <c r="AA449" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="AB449" t="s" s="2">
         <v>22</v>
@@ -58269,7 +58277,7 @@
     </row>
     <row r="450">
       <c r="A450" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B450" t="s" s="2">
         <v>808</v>
@@ -58378,7 +58386,7 @@
     </row>
     <row r="451">
       <c r="A451" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B451" t="s" s="2">
         <v>809</v>
@@ -58481,7 +58489,7 @@
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B452" t="s" s="2">
         <v>811</v>
@@ -58586,7 +58594,7 @@
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B453" t="s" s="2">
         <v>813</v>
@@ -58693,7 +58701,7 @@
     </row>
     <row r="454">
       <c r="A454" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B454" t="s" s="2">
         <v>815</v>
@@ -58798,7 +58806,7 @@
     </row>
     <row r="455">
       <c r="A455" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B455" t="s" s="2">
         <v>817</v>
@@ -58903,7 +58911,7 @@
     </row>
     <row r="456">
       <c r="A456" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B456" t="s" s="2">
         <v>819</v>
@@ -59008,7 +59016,7 @@
     </row>
     <row r="457">
       <c r="A457" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B457" t="s" s="2">
         <v>821</v>
@@ -59115,7 +59123,7 @@
     </row>
     <row r="458">
       <c r="A458" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B458" t="s" s="2">
         <v>823</v>
@@ -59222,7 +59230,7 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B459" t="s" s="2">
         <v>824</v>
@@ -59327,7 +59335,7 @@
     </row>
     <row r="460">
       <c r="A460" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B460" t="s" s="2">
         <v>829</v>
@@ -59432,7 +59440,7 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B461" t="s" s="2">
         <v>834</v>
@@ -59539,7 +59547,7 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B462" t="s" s="2">
         <v>842</v>
@@ -59642,7 +59650,7 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B463" t="s" s="2">
         <v>843</v>
@@ -59747,7 +59755,7 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B464" t="s" s="2">
         <v>844</v>
@@ -59854,7 +59862,7 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B465" t="s" s="2">
         <v>849</v>
@@ -59957,7 +59965,7 @@
     </row>
     <row r="466">
       <c r="A466" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B466" t="s" s="2">
         <v>854</v>
@@ -60060,7 +60068,7 @@
     </row>
     <row r="467">
       <c r="A467" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B467" t="s" s="2">
         <v>857</v>
@@ -60167,7 +60175,7 @@
     </row>
     <row r="468">
       <c r="A468" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B468" t="s" s="2">
         <v>864</v>
@@ -60274,7 +60282,7 @@
     </row>
     <row r="469">
       <c r="A469" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B469" t="s" s="2">
         <v>871</v>
@@ -60379,7 +60387,7 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B470" t="s" s="2">
         <v>876</v>
@@ -60482,7 +60490,7 @@
     </row>
     <row r="471">
       <c r="A471" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B471" t="s" s="2">
         <v>879</v>
@@ -60585,7 +60593,7 @@
     </row>
     <row r="472">
       <c r="A472" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B472" t="s" s="2">
         <v>885</v>
@@ -60692,16 +60700,16 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C473" t="s" s="2">
         <v>879</v>
       </c>
       <c r="D473" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E473" t="s" s="2">
         <v>22</v>
@@ -60723,7 +60731,7 @@
         <v>107</v>
       </c>
       <c r="L473" t="s" s="2">
-        <v>880</v>
+        <v>966</v>
       </c>
       <c r="M473" t="s" s="2">
         <v>881</v>
@@ -60799,7 +60807,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B474" t="s" s="2">
         <v>887</v>
@@ -60904,7 +60912,7 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B475" t="s" s="2">
         <v>892</v>
@@ -61011,7 +61019,7 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B476" t="s" s="2">
         <v>897</v>
@@ -61114,7 +61122,7 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B477" t="s" s="2">
         <v>898</v>
@@ -61219,7 +61227,7 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B478" t="s" s="2">
         <v>899</v>
@@ -61326,7 +61334,7 @@
     </row>
     <row r="479">
       <c r="A479" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B479" t="s" s="2">
         <v>900</v>
@@ -61433,7 +61441,7 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B480" t="s" s="2">
         <v>906</v>
@@ -61540,7 +61548,7 @@
     </row>
     <row r="481">
       <c r="A481" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B481" t="s" s="2">
         <v>910</v>
@@ -61647,7 +61655,7 @@
     </row>
     <row r="482">
       <c r="A482" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B482" t="s" s="2">
         <v>915</v>
@@ -61754,7 +61762,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B483" t="s" s="2">
         <v>917</v>
@@ -61861,7 +61869,7 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B484" t="s" s="2">
         <v>921</v>
@@ -61964,7 +61972,7 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B485" t="s" s="2">
         <v>922</v>
@@ -62069,7 +62077,7 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B486" t="s" s="2">
         <v>923</v>
@@ -62176,7 +62184,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B487" t="s" s="2">
         <v>924</v>
@@ -62279,7 +62287,7 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B488" t="s" s="2">
         <v>925</v>
@@ -62382,7 +62390,7 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B489" t="s" s="2">
         <v>926</v>
@@ -62489,7 +62497,7 @@
     </row>
     <row r="490">
       <c r="A490" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B490" t="s" s="2">
         <v>928</v>
@@ -62596,7 +62604,7 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B491" t="s" s="2">
         <v>930</v>
@@ -62701,7 +62709,7 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B492" t="s" s="2">
         <v>931</v>
@@ -62804,13 +62812,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -62836,13 +62844,13 @@
         <v>78</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="O493" t="s" s="2">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="P493" s="2"/>
       <c r="Q493" t="s" s="2">
@@ -62892,7 +62900,7 @@
         <v>22</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>76</v>
@@ -62904,18 +62912,18 @@
         <v>82</v>
       </c>
       <c r="AK493" t="s" s="2">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -63012,13 +63020,13 @@
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -63117,13 +63125,13 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
@@ -63149,13 +63157,13 @@
         <v>117</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="O496" t="s" s="2">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="P496" s="2"/>
       <c r="Q496" t="s" s="2">
@@ -63205,7 +63213,7 @@
         <v>22</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>76</v>
@@ -63214,7 +63222,7 @@
         <v>85</v>
       </c>
       <c r="AJ496" t="s" s="2">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="AK496" t="s" s="2">
         <v>83</v>
@@ -63222,13 +63230,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -63254,20 +63262,20 @@
         <v>117</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="O497" t="s" s="2">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="P497" s="2"/>
       <c r="Q497" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R497" t="s" s="2">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="S497" t="s" s="2">
         <v>22</v>
@@ -63312,7 +63320,7 @@
         <v>22</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>76</v>
@@ -63321,7 +63329,7 @@
         <v>85</v>
       </c>
       <c r="AJ497" t="s" s="2">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="AK497" t="s" s="2">
         <v>83</v>
@@ -63329,13 +63337,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -63361,10 +63369,10 @@
         <v>78</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="N498" t="s" s="2">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="O498" t="s" s="2">
         <v>405</v>
@@ -63417,7 +63425,7 @@
         <v>22</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>76</v>
@@ -63429,18 +63437,18 @@
         <v>82</v>
       </c>
       <c r="AK498" t="s" s="2">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -63537,13 +63545,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
@@ -63642,13 +63650,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D501" t="s" s="2">
         <v>410</v>
@@ -63676,10 +63684,10 @@
         <v>411</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="O501" s="2"/>
       <c r="P501" s="2"/>
@@ -63747,7 +63755,7 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B502" t="s" s="2">
         <v>420</v>
@@ -63782,7 +63790,7 @@
         <v>416</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="O502" t="s" s="2">
         <v>418</v>
@@ -63854,13 +63862,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -63957,13 +63965,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -64058,13 +64066,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D505" t="s" s="2">
         <v>388</v>
@@ -64165,13 +64173,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B506" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="C506" t="s" s="2">
         <v>1007</v>
-      </c>
-      <c r="C506" t="s" s="2">
-        <v>1005</v>
       </c>
       <c r="D506" t="s" s="2">
         <v>425</v>
@@ -64199,10 +64207,10 @@
         <v>426</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="O506" s="2"/>
       <c r="P506" s="2"/>
@@ -64270,13 +64278,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -64373,7 +64381,7 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B508" t="s" s="2">
         <v>437</v>
@@ -64480,7 +64488,7 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B509" t="s" s="2">
         <v>442</v>
@@ -64585,7 +64593,7 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B510" t="s" s="2">
         <v>447</v>
@@ -64690,7 +64698,7 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B511" t="s" s="2">
         <v>454</v>
@@ -64797,7 +64805,7 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B512" t="s" s="2">
         <v>130</v>
@@ -64829,10 +64837,10 @@
         <v>78</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="O512" s="2"/>
       <c r="P512" s="2"/>
@@ -64900,7 +64908,7 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B513" t="s" s="2">
         <v>134</v>
@@ -65003,7 +65011,7 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B514" t="s" s="2">
         <v>135</v>
@@ -65106,7 +65114,7 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B515" t="s" s="2">
         <v>137</v>
@@ -65152,7 +65160,7 @@
       </c>
       <c r="R515" s="2"/>
       <c r="S515" t="s" s="2">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="T515" t="s" s="2">
         <v>22</v>
@@ -65211,7 +65219,7 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B516" t="s" s="2">
         <v>142</v>
@@ -65243,10 +65251,10 @@
         <v>86</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="O516" s="2"/>
       <c r="P516" s="2"/>
@@ -65314,7 +65322,7 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B517" t="s" s="2">
         <v>130</v>
@@ -65346,10 +65354,10 @@
         <v>78</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="N517" t="s" s="2">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="O517" s="2"/>
       <c r="P517" s="2"/>
@@ -65417,7 +65425,7 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B518" t="s" s="2">
         <v>134</v>
@@ -65520,7 +65528,7 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B519" t="s" s="2">
         <v>135</v>
@@ -65623,7 +65631,7 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B520" t="s" s="2">
         <v>137</v>
@@ -65669,7 +65677,7 @@
       </c>
       <c r="R520" s="2"/>
       <c r="S520" t="s" s="2">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="T520" t="s" s="2">
         <v>22</v>
@@ -65728,7 +65736,7 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B521" t="s" s="2">
         <v>142</v>
@@ -65760,10 +65768,10 @@
         <v>86</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" s="2"/>
@@ -65831,13 +65839,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -65863,13 +65871,13 @@
         <v>78</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="O522" t="s" s="2">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="P522" s="2"/>
       <c r="Q522" t="s" s="2">
@@ -65919,7 +65927,7 @@
         <v>22</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>76</v>
@@ -65931,18 +65939,18 @@
         <v>82</v>
       </c>
       <c r="AK522" t="s" s="2">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -66039,13 +66047,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -66144,13 +66152,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -66176,13 +66184,13 @@
         <v>850</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="O525" t="s" s="2">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="P525" s="2"/>
       <c r="Q525" t="s" s="2">
@@ -66232,7 +66240,7 @@
         <v>22</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>76</v>
@@ -66249,13 +66257,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -66281,13 +66289,13 @@
         <v>850</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="O526" t="s" s="2">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="P526" s="2"/>
       <c r="Q526" t="s" s="2">
@@ -66337,7 +66345,7 @@
         <v>22</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
@@ -66354,13 +66362,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -66386,13 +66394,13 @@
         <v>78</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="O527" t="s" s="2">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="P527" s="2"/>
       <c r="Q527" t="s" s="2">
@@ -66442,7 +66450,7 @@
         <v>22</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>76</v>
@@ -66454,18 +66462,18 @@
         <v>82</v>
       </c>
       <c r="AK527" t="s" s="2">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -66562,13 +66570,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -66667,13 +66675,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -66696,13 +66704,13 @@
         <v>107</v>
       </c>
       <c r="L530" t="s" s="2">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="O530" s="2"/>
       <c r="P530" s="2"/>
@@ -66753,7 +66761,7 @@
         <v>22</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>76</v>
@@ -66770,13 +66778,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -66799,13 +66807,13 @@
         <v>107</v>
       </c>
       <c r="L531" t="s" s="2">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="O531" s="2"/>
       <c r="P531" s="2"/>
@@ -66856,7 +66864,7 @@
         <v>22</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>76</v>
@@ -66873,13 +66881,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -66905,13 +66913,13 @@
         <v>78</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="O532" t="s" s="2">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="P532" s="2"/>
       <c r="Q532" t="s" s="2">
@@ -66961,7 +66969,7 @@
         <v>22</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>76</v>
@@ -66973,18 +66981,18 @@
         <v>82</v>
       </c>
       <c r="AK532" t="s" s="2">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -67081,13 +67089,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -67186,16 +67194,16 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="D535" t="s" s="2">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="E535" t="s" s="2">
         <v>22</v>
@@ -67217,13 +67225,13 @@
         <v>22</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="O535" s="2"/>
       <c r="P535" s="2"/>
@@ -67291,13 +67299,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -67323,13 +67331,13 @@
         <v>86</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="O536" t="s" s="2">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="P536" s="2"/>
       <c r="Q536" t="s" s="2">
@@ -67379,7 +67387,7 @@
         <v>22</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>76</v>
@@ -67388,7 +67396,7 @@
         <v>85</v>
       </c>
       <c r="AJ536" t="s" s="2">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AK536" t="s" s="2">
         <v>83</v>
@@ -67396,13 +67404,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -67428,13 +67436,13 @@
         <v>138</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="O537" t="s" s="2">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="P537" s="2"/>
       <c r="Q537" t="s" s="2">
@@ -67463,10 +67471,10 @@
         <v>239</v>
       </c>
       <c r="Z537" t="s" s="2">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="AA537" t="s" s="2">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="AB537" t="s" s="2">
         <v>22</v>
@@ -67484,7 +67492,7 @@
         <v>22</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>76</v>
@@ -67501,13 +67509,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -67533,13 +67541,13 @@
         <v>621</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="N538" t="s" s="2">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="O538" t="s" s="2">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="P538" s="2"/>
       <c r="Q538" t="s" s="2">
@@ -67589,7 +67597,7 @@
         <v>22</v>
       </c>
       <c r="AG538" t="s" s="2">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="AH538" t="s" s="2">
         <v>76</v>
@@ -67606,13 +67614,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -67638,13 +67646,13 @@
         <v>86</v>
       </c>
       <c r="M539" t="s" s="2">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="N539" t="s" s="2">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="O539" t="s" s="2">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="P539" s="2"/>
       <c r="Q539" t="s" s="2">
@@ -67694,7 +67702,7 @@
         <v>22</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>76</v>
@@ -67711,7 +67719,7 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B540" t="s" s="2">
         <v>130</v>
@@ -67743,10 +67751,10 @@
         <v>78</v>
       </c>
       <c r="M540" t="s" s="2">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="N540" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="O540" s="2"/>
       <c r="P540" s="2"/>
@@ -67814,7 +67822,7 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B541" t="s" s="2">
         <v>134</v>
@@ -67917,7 +67925,7 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B542" t="s" s="2">
         <v>135</v>
@@ -68020,7 +68028,7 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B543" t="s" s="2">
         <v>137</v>
@@ -68066,7 +68074,7 @@
       </c>
       <c r="R543" s="2"/>
       <c r="S543" t="s" s="2">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="T543" t="s" s="2">
         <v>22</v>
@@ -68125,7 +68133,7 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B544" t="s" s="2">
         <v>142</v>
@@ -68157,13 +68165,13 @@
         <v>236</v>
       </c>
       <c r="M544" t="s" s="2">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="N544" t="s" s="2">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="O544" t="s" s="2">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="P544" s="2"/>
       <c r="Q544" t="s" s="2">
@@ -68230,13 +68238,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -68262,13 +68270,13 @@
         <v>78</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="N545" t="s" s="2">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="O545" t="s" s="2">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="P545" s="2"/>
       <c r="Q545" t="s" s="2">
@@ -68318,7 +68326,7 @@
         <v>22</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
@@ -68335,13 +68343,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -68438,13 +68446,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -68543,13 +68551,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -68575,10 +68583,10 @@
         <v>850</v>
       </c>
       <c r="M548" t="s" s="2">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="N548" t="s" s="2">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="O548" s="2"/>
       <c r="P548" s="2"/>
@@ -68629,7 +68637,7 @@
         <v>22</v>
       </c>
       <c r="AG548" t="s" s="2">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="AH548" t="s" s="2">
         <v>85</v>
@@ -68646,13 +68654,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -68678,13 +68686,13 @@
         <v>415</v>
       </c>
       <c r="M549" t="s" s="2">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="N549" t="s" s="2">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="O549" t="s" s="2">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="P549" s="2"/>
       <c r="Q549" t="s" s="2">
@@ -68734,7 +68742,7 @@
         <v>22</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>85</v>
@@ -68751,13 +68759,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -68783,10 +68791,10 @@
         <v>415</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="O550" s="2"/>
       <c r="P550" s="2"/>
@@ -68794,7 +68802,7 @@
         <v>22</v>
       </c>
       <c r="R550" t="s" s="2">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="S550" t="s" s="2">
         <v>22</v>
@@ -68839,7 +68847,7 @@
         <v>22</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>76</v>
@@ -68856,13 +68864,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -68888,10 +68896,10 @@
         <v>415</v>
       </c>
       <c r="M551" t="s" s="2">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="N551" t="s" s="2">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="O551" s="2"/>
       <c r="P551" s="2"/>
@@ -68942,7 +68950,7 @@
         <v>22</v>
       </c>
       <c r="AG551" t="s" s="2">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="AH551" t="s" s="2">
         <v>76</v>
@@ -68959,13 +68967,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -68991,10 +68999,10 @@
         <v>415</v>
       </c>
       <c r="M552" t="s" s="2">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="N552" t="s" s="2">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="O552" s="2"/>
       <c r="P552" s="2"/>
@@ -69045,7 +69053,7 @@
         <v>22</v>
       </c>
       <c r="AG552" t="s" s="2">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>76</v>
@@ -69062,13 +69070,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -69091,16 +69099,16 @@
         <v>107</v>
       </c>
       <c r="L553" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="M553" t="s" s="2">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="N553" t="s" s="2">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="O553" t="s" s="2">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="P553" s="2"/>
       <c r="Q553" t="s" s="2">
@@ -69150,7 +69158,7 @@
         <v>22</v>
       </c>
       <c r="AG553" t="s" s="2">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="AH553" t="s" s="2">
         <v>85</v>
@@ -69167,13 +69175,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -69199,13 +69207,13 @@
         <v>86</v>
       </c>
       <c r="M554" t="s" s="2">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="N554" t="s" s="2">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="O554" t="s" s="2">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="P554" s="2"/>
       <c r="Q554" t="s" s="2">
@@ -69255,7 +69263,7 @@
         <v>22</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -69272,17 +69280,17 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="F555" s="2"/>
       <c r="G555" t="s" s="2">
@@ -69304,10 +69312,10 @@
         <v>78</v>
       </c>
       <c r="M555" t="s" s="2">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="N555" t="s" s="2">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -69358,7 +69366,7 @@
         <v>22</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -69370,18 +69378,18 @@
         <v>22</v>
       </c>
       <c r="AK555" t="s" s="2">
-        <v>1167</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -69480,13 +69488,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -69583,13 +69591,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -69688,13 +69696,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -69793,13 +69801,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -69898,13 +69906,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -70003,13 +70011,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -70038,7 +70046,7 @@
         <v>93</v>
       </c>
       <c r="N562" t="s" s="2">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="O562" t="s" s="2">
         <v>95</v>
@@ -70108,13 +70116,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -70215,13 +70223,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -70247,13 +70255,13 @@
         <v>621</v>
       </c>
       <c r="M564" t="s" s="2">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="N564" t="s" s="2">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="O564" t="s" s="2">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="P564" s="2"/>
       <c r="Q564" t="s" s="2">
@@ -70301,7 +70309,7 @@
         <v>98</v>
       </c>
       <c r="AG564" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="AH564" t="s" s="2">
         <v>76</v>
@@ -70318,13 +70326,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D565" t="s" s="2">
         <v>627</v>
@@ -70352,13 +70360,13 @@
         <v>621</v>
       </c>
       <c r="M565" t="s" s="2">
+        <v>1184</v>
+      </c>
+      <c r="N565" t="s" s="2">
+        <v>1185</v>
+      </c>
+      <c r="O565" t="s" s="2">
         <v>1182</v>
-      </c>
-      <c r="N565" t="s" s="2">
-        <v>1183</v>
-      </c>
-      <c r="O565" t="s" s="2">
-        <v>1180</v>
       </c>
       <c r="P565" s="2"/>
       <c r="Q565" t="s" s="2">
@@ -70408,7 +70416,7 @@
         <v>22</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>76</v>
@@ -70425,13 +70433,13 @@
     </row>
     <row r="566">
       <c r="A566" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" t="s" s="2">
@@ -70528,13 +70536,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" t="s" s="2">
@@ -70633,13 +70641,13 @@
     </row>
     <row r="568">
       <c r="A568" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D568" s="2"/>
       <c r="E568" t="s" s="2">
@@ -70740,13 +70748,13 @@
     </row>
     <row r="569">
       <c r="A569" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="D569" s="2"/>
       <c r="E569" t="s" s="2">
@@ -70847,13 +70855,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D570" s="2"/>
       <c r="E570" t="s" s="2">
@@ -70954,13 +70962,13 @@
     </row>
     <row r="571">
       <c r="A571" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D571" s="2"/>
       <c r="E571" t="s" s="2">
@@ -71059,13 +71067,13 @@
     </row>
     <row r="572">
       <c r="A572" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D572" s="2"/>
       <c r="E572" t="s" s="2">
@@ -71162,13 +71170,13 @@
     </row>
     <row r="573">
       <c r="A573" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D573" s="2"/>
       <c r="E573" t="s" s="2">
@@ -71267,13 +71275,13 @@
     </row>
     <row r="574">
       <c r="A574" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B574" t="s" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="C574" t="s" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D574" s="2"/>
       <c r="E574" t="s" s="2">
@@ -71296,16 +71304,16 @@
         <v>107</v>
       </c>
       <c r="L574" t="s" s="2">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="M574" t="s" s="2">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="N574" t="s" s="2">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="O574" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="P574" s="2"/>
       <c r="Q574" t="s" s="2">
@@ -71355,7 +71363,7 @@
         <v>22</v>
       </c>
       <c r="AG574" t="s" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="AH574" t="s" s="2">
         <v>76</v>
@@ -71372,13 +71380,13 @@
     </row>
     <row r="575">
       <c r="A575" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B575" t="s" s="2">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C575" t="s" s="2">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D575" s="2"/>
       <c r="E575" t="s" s="2">
@@ -71404,13 +71412,13 @@
         <v>138</v>
       </c>
       <c r="M575" t="s" s="2">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="N575" t="s" s="2">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="O575" t="s" s="2">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="P575" s="2"/>
       <c r="Q575" t="s" s="2">
@@ -71460,7 +71468,7 @@
         <v>22</v>
       </c>
       <c r="AG575" t="s" s="2">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="AH575" t="s" s="2">
         <v>76</v>
@@ -71477,17 +71485,17 @@
     </row>
     <row r="576">
       <c r="A576" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B576" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C576" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D576" s="2"/>
       <c r="E576" t="s" s="2">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="F576" s="2"/>
       <c r="G576" t="s" s="2">
@@ -71506,13 +71514,13 @@
         <v>107</v>
       </c>
       <c r="L576" t="s" s="2">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="M576" t="s" s="2">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="N576" t="s" s="2">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="O576" s="2"/>
       <c r="P576" s="2"/>
@@ -71563,7 +71571,7 @@
         <v>22</v>
       </c>
       <c r="AG576" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="AH576" t="s" s="2">
         <v>76</v>
@@ -71580,17 +71588,17 @@
     </row>
     <row r="577">
       <c r="A577" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B577" t="s" s="2">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="C577" t="s" s="2">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D577" s="2"/>
       <c r="E577" t="s" s="2">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="F577" s="2"/>
       <c r="G577" t="s" s="2">
@@ -71609,13 +71617,13 @@
         <v>107</v>
       </c>
       <c r="L577" t="s" s="2">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="M577" t="s" s="2">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="N577" t="s" s="2">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="O577" s="2"/>
       <c r="P577" s="2"/>
@@ -71666,7 +71674,7 @@
         <v>22</v>
       </c>
       <c r="AG577" t="s" s="2">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="AH577" t="s" s="2">
         <v>76</v>
@@ -71683,17 +71691,17 @@
     </row>
     <row r="578">
       <c r="A578" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B578" t="s" s="2">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C578" t="s" s="2">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D578" s="2"/>
       <c r="E578" t="s" s="2">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="F578" s="2"/>
       <c r="G578" t="s" s="2">
@@ -71715,16 +71723,16 @@
         <v>621</v>
       </c>
       <c r="M578" t="s" s="2">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="N578" t="s" s="2">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="O578" t="s" s="2">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="P578" t="s" s="2">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="Q578" t="s" s="2">
         <v>22</v>
@@ -71773,7 +71781,7 @@
         <v>22</v>
       </c>
       <c r="AG578" t="s" s="2">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="AH578" t="s" s="2">
         <v>76</v>
@@ -71790,13 +71798,13 @@
     </row>
     <row r="579">
       <c r="A579" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B579" t="s" s="2">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C579" t="s" s="2">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="D579" s="2"/>
       <c r="E579" t="s" s="2">
@@ -71822,13 +71830,13 @@
         <v>172</v>
       </c>
       <c r="M579" t="s" s="2">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="N579" t="s" s="2">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="O579" t="s" s="2">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="P579" s="2"/>
       <c r="Q579" t="s" s="2">
@@ -71857,10 +71865,10 @@
         <v>177</v>
       </c>
       <c r="Z579" t="s" s="2">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="AA579" t="s" s="2">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="AB579" t="s" s="2">
         <v>22</v>
@@ -71878,7 +71886,7 @@
         <v>22</v>
       </c>
       <c r="AG579" t="s" s="2">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="AH579" t="s" s="2">
         <v>85</v>
@@ -71895,13 +71903,13 @@
     </row>
     <row r="580">
       <c r="A580" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C580" t="s" s="2">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D580" s="2"/>
       <c r="E580" t="s" s="2">
@@ -71927,13 +71935,13 @@
         <v>172</v>
       </c>
       <c r="M580" t="s" s="2">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="N580" t="s" s="2">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="O580" t="s" s="2">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="P580" s="2"/>
       <c r="Q580" t="s" s="2">
@@ -71962,10 +71970,10 @@
         <v>177</v>
       </c>
       <c r="Z580" t="s" s="2">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="AA580" t="s" s="2">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="AB580" t="s" s="2">
         <v>22</v>
@@ -71983,7 +71991,7 @@
         <v>22</v>
       </c>
       <c r="AG580" t="s" s="2">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="AH580" t="s" s="2">
         <v>85</v>
@@ -72000,13 +72008,13 @@
     </row>
     <row r="581">
       <c r="A581" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="C581" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D581" s="2"/>
       <c r="E581" t="s" s="2">
@@ -72032,16 +72040,16 @@
         <v>236</v>
       </c>
       <c r="M581" t="s" s="2">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="N581" t="s" s="2">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="O581" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="P581" t="s" s="2">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="Q581" t="s" s="2">
         <v>22</v>
@@ -72069,10 +72077,10 @@
         <v>579</v>
       </c>
       <c r="Z581" t="s" s="2">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="AA581" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="AB581" t="s" s="2">
         <v>22</v>
@@ -72088,7 +72096,7 @@
         <v>98</v>
       </c>
       <c r="AG581" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="AH581" t="s" s="2">
         <v>76</v>
@@ -72105,13 +72113,13 @@
     </row>
     <row r="582">
       <c r="A582" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B582" t="s" s="2">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="C582" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D582" t="s" s="2">
         <v>674</v>
@@ -72139,16 +72147,16 @@
         <v>236</v>
       </c>
       <c r="M582" t="s" s="2">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="N582" t="s" s="2">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="O582" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="P582" t="s" s="2">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="Q582" t="s" s="2">
         <v>22</v>
@@ -72176,10 +72184,10 @@
         <v>177</v>
       </c>
       <c r="Z582" t="s" s="2">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="AA582" t="s" s="2">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="AB582" t="s" s="2">
         <v>22</v>
@@ -72197,7 +72205,7 @@
         <v>22</v>
       </c>
       <c r="AG582" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="AH582" t="s" s="2">
         <v>76</v>
@@ -72214,16 +72222,16 @@
     </row>
     <row r="583">
       <c r="A583" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B583" t="s" s="2">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="C583" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D583" t="s" s="2">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E583" t="s" s="2">
         <v>22</v>
@@ -72248,16 +72256,16 @@
         <v>236</v>
       </c>
       <c r="M583" t="s" s="2">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="N583" t="s" s="2">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="O583" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="P583" t="s" s="2">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="Q583" t="s" s="2">
         <v>22</v>
@@ -72286,7 +72294,7 @@
       </c>
       <c r="Z583" s="2"/>
       <c r="AA583" t="s" s="2">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="AB583" t="s" s="2">
         <v>22</v>
@@ -72304,7 +72312,7 @@
         <v>22</v>
       </c>
       <c r="AG583" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="AH583" t="s" s="2">
         <v>76</v>
@@ -72321,16 +72329,16 @@
     </row>
     <row r="584">
       <c r="A584" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B584" t="s" s="2">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C584" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D584" t="s" s="2">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E584" t="s" s="2">
         <v>22</v>
@@ -72355,16 +72363,16 @@
         <v>236</v>
       </c>
       <c r="M584" t="s" s="2">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="N584" t="s" s="2">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="O584" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="P584" t="s" s="2">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="Q584" t="s" s="2">
         <v>22</v>
@@ -72393,7 +72401,7 @@
       </c>
       <c r="Z584" s="2"/>
       <c r="AA584" t="s" s="2">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="AB584" t="s" s="2">
         <v>22</v>
@@ -72411,7 +72419,7 @@
         <v>22</v>
       </c>
       <c r="AG584" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="AH584" t="s" s="2">
         <v>76</v>
@@ -72428,13 +72436,13 @@
     </row>
     <row r="585">
       <c r="A585" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C585" t="s" s="2">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D585" s="2"/>
       <c r="E585" t="s" s="2">
@@ -72460,10 +72468,10 @@
         <v>172</v>
       </c>
       <c r="M585" t="s" s="2">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="N585" t="s" s="2">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="O585" s="2"/>
       <c r="P585" s="2"/>
@@ -72471,7 +72479,7 @@
         <v>22</v>
       </c>
       <c r="R585" t="s" s="2">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="S585" t="s" s="2">
         <v>22</v>
@@ -72495,10 +72503,10 @@
         <v>177</v>
       </c>
       <c r="Z585" t="s" s="2">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="AA585" t="s" s="2">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="AB585" t="s" s="2">
         <v>22</v>
@@ -72516,7 +72524,7 @@
         <v>22</v>
       </c>
       <c r="AG585" t="s" s="2">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="AH585" t="s" s="2">
         <v>76</v>
@@ -72533,13 +72541,13 @@
     </row>
     <row r="586">
       <c r="A586" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B586" t="s" s="2">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="C586" t="s" s="2">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="D586" s="2"/>
       <c r="E586" t="s" s="2">
@@ -72565,67 +72573,67 @@
         <v>298</v>
       </c>
       <c r="M586" t="s" s="2">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="N586" t="s" s="2">
+        <v>1269</v>
+      </c>
+      <c r="O586" t="s" s="2">
+        <v>1270</v>
+      </c>
+      <c r="P586" t="s" s="2">
+        <v>1271</v>
+      </c>
+      <c r="Q586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R586" t="s" s="2">
+        <v>1272</v>
+      </c>
+      <c r="S586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG586" t="s" s="2">
         <v>1267</v>
-      </c>
-      <c r="O586" t="s" s="2">
-        <v>1268</v>
-      </c>
-      <c r="P586" t="s" s="2">
-        <v>1269</v>
-      </c>
-      <c r="Q586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R586" t="s" s="2">
-        <v>1270</v>
-      </c>
-      <c r="S586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF586" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG586" t="s" s="2">
-        <v>1265</v>
       </c>
       <c r="AH586" t="s" s="2">
         <v>76</v>
@@ -72642,17 +72650,17 @@
     </row>
     <row r="587">
       <c r="A587" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B587" t="s" s="2">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="C587" t="s" s="2">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D587" s="2"/>
       <c r="E587" t="s" s="2">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="F587" s="2"/>
       <c r="G587" t="s" s="2">
@@ -72674,13 +72682,13 @@
         <v>236</v>
       </c>
       <c r="M587" t="s" s="2">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="N587" t="s" s="2">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="O587" t="s" s="2">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="P587" s="2"/>
       <c r="Q587" t="s" s="2">
@@ -72710,7 +72718,7 @@
       </c>
       <c r="Z587" s="2"/>
       <c r="AA587" t="s" s="2">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="AB587" t="s" s="2">
         <v>22</v>
@@ -72728,7 +72736,7 @@
         <v>22</v>
       </c>
       <c r="AG587" t="s" s="2">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="AH587" t="s" s="2">
         <v>76</v>
@@ -72737,7 +72745,7 @@
         <v>85</v>
       </c>
       <c r="AJ587" t="s" s="2">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="AK587" t="s" s="2">
         <v>83</v>
@@ -72745,13 +72753,13 @@
     </row>
     <row r="588">
       <c r="A588" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C588" t="s" s="2">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="D588" s="2"/>
       <c r="E588" t="s" s="2">
@@ -72848,13 +72856,13 @@
     </row>
     <row r="589">
       <c r="A589" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="C589" t="s" s="2">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D589" s="2"/>
       <c r="E589" t="s" s="2">
@@ -72953,16 +72961,16 @@
     </row>
     <row r="590">
       <c r="A590" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C590" t="s" s="2">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D590" t="s" s="2">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E590" t="s" s="2">
         <v>22</v>
@@ -72984,16 +72992,16 @@
         <v>22</v>
       </c>
       <c r="L590" t="s" s="2">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="M590" t="s" s="2">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="N590" t="s" s="2">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="O590" t="s" s="2">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="P590" s="2"/>
       <c r="Q590" t="s" s="2">
@@ -73052,7 +73060,7 @@
         <v>77</v>
       </c>
       <c r="AJ590" t="s" s="2">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="AK590" t="s" s="2">
         <v>100</v>
@@ -73060,13 +73068,13 @@
     </row>
     <row r="591">
       <c r="A591" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C591" t="s" s="2">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D591" s="2"/>
       <c r="E591" t="s" s="2">
@@ -73167,13 +73175,13 @@
     </row>
     <row r="592">
       <c r="A592" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B592" t="s" s="2">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C592" t="s" s="2">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D592" s="2"/>
       <c r="E592" t="s" s="2">
@@ -73202,7 +73210,7 @@
         <v>305</v>
       </c>
       <c r="N592" t="s" s="2">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="O592" t="s" s="2">
         <v>307</v>
@@ -73274,17 +73282,17 @@
     </row>
     <row r="593">
       <c r="A593" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B593" t="s" s="2">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="C593" t="s" s="2">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D593" s="2"/>
       <c r="E593" t="s" s="2">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="F593" s="2"/>
       <c r="G593" t="s" s="2">
@@ -73306,13 +73314,13 @@
         <v>236</v>
       </c>
       <c r="M593" t="s" s="2">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="N593" t="s" s="2">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="O593" t="s" s="2">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="P593" s="2"/>
       <c r="Q593" t="s" s="2">
@@ -73341,10 +73349,10 @@
         <v>579</v>
       </c>
       <c r="Z593" t="s" s="2">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="AA593" t="s" s="2">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="AB593" t="s" s="2">
         <v>22</v>
@@ -73362,7 +73370,7 @@
         <v>22</v>
       </c>
       <c r="AG593" t="s" s="2">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="AH593" t="s" s="2">
         <v>76</v>
@@ -73371,7 +73379,7 @@
         <v>77</v>
       </c>
       <c r="AJ593" t="s" s="2">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="AK593" t="s" s="2">
         <v>83</v>
@@ -73379,13 +73387,13 @@
     </row>
     <row r="594">
       <c r="A594" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B594" t="s" s="2">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="C594" t="s" s="2">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D594" s="2"/>
       <c r="E594" t="s" s="2">
@@ -73408,17 +73416,17 @@
         <v>107</v>
       </c>
       <c r="L594" t="s" s="2">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="M594" t="s" s="2">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="N594" t="s" s="2">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="O594" s="2"/>
       <c r="P594" t="s" s="2">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="Q594" t="s" s="2">
         <v>22</v>
@@ -73467,7 +73475,7 @@
         <v>22</v>
       </c>
       <c r="AG594" t="s" s="2">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="AH594" t="s" s="2">
         <v>76</v>
@@ -73484,13 +73492,13 @@
     </row>
     <row r="595">
       <c r="A595" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B595" t="s" s="2">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C595" t="s" s="2">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="D595" s="2"/>
       <c r="E595" t="s" s="2">
@@ -73516,10 +73524,10 @@
         <v>724</v>
       </c>
       <c r="M595" t="s" s="2">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="N595" t="s" s="2">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="O595" s="2"/>
       <c r="P595" s="2"/>
@@ -73570,7 +73578,7 @@
         <v>22</v>
       </c>
       <c r="AG595" t="s" s="2">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="AH595" t="s" s="2">
         <v>85</v>
@@ -73587,17 +73595,17 @@
     </row>
     <row r="596">
       <c r="A596" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B596" t="s" s="2">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C596" t="s" s="2">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="D596" s="2"/>
       <c r="E596" t="s" s="2">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="F596" s="2"/>
       <c r="G596" t="s" s="2">
@@ -73619,10 +73627,10 @@
         <v>736</v>
       </c>
       <c r="M596" t="s" s="2">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="N596" t="s" s="2">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="O596" s="2"/>
       <c r="P596" s="2"/>
@@ -73673,7 +73681,7 @@
         <v>22</v>
       </c>
       <c r="AG596" t="s" s="2">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="AH596" t="s" s="2">
         <v>76</v>
@@ -73690,17 +73698,17 @@
     </row>
     <row r="597">
       <c r="A597" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B597" t="s" s="2">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C597" t="s" s="2">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D597" s="2"/>
       <c r="E597" t="s" s="2">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="F597" s="2"/>
       <c r="G597" t="s" s="2">
@@ -73719,13 +73727,13 @@
         <v>107</v>
       </c>
       <c r="L597" t="s" s="2">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="M597" t="s" s="2">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="N597" t="s" s="2">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="O597" s="2"/>
       <c r="P597" s="2"/>
@@ -73776,7 +73784,7 @@
         <v>22</v>
       </c>
       <c r="AG597" t="s" s="2">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="AH597" t="s" s="2">
         <v>76</v>
@@ -73793,13 +73801,13 @@
     </row>
     <row r="598">
       <c r="A598" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B598" t="s" s="2">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="C598" t="s" s="2">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D598" s="2"/>
       <c r="E598" t="s" s="2">
@@ -73822,13 +73830,13 @@
         <v>107</v>
       </c>
       <c r="L598" t="s" s="2">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="M598" t="s" s="2">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="N598" t="s" s="2">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="O598" s="2"/>
       <c r="P598" s="2"/>
@@ -73858,10 +73866,10 @@
         <v>579</v>
       </c>
       <c r="Z598" t="s" s="2">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="AA598" t="s" s="2">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="AB598" t="s" s="2">
         <v>22</v>
@@ -73879,7 +73887,7 @@
         <v>22</v>
       </c>
       <c r="AG598" t="s" s="2">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="AH598" t="s" s="2">
         <v>76</v>
@@ -73896,17 +73904,17 @@
     </row>
     <row r="599">
       <c r="A599" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B599" t="s" s="2">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="C599" t="s" s="2">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="D599" s="2"/>
       <c r="E599" t="s" s="2">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="F599" s="2"/>
       <c r="G599" t="s" s="2">
@@ -73928,10 +73936,10 @@
         <v>117</v>
       </c>
       <c r="M599" t="s" s="2">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="N599" t="s" s="2">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="O599" s="2"/>
       <c r="P599" s="2"/>
@@ -73982,7 +73990,7 @@
         <v>22</v>
       </c>
       <c r="AG599" t="s" s="2">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="AH599" t="s" s="2">
         <v>76</v>
@@ -73999,17 +74007,17 @@
     </row>
     <row r="600">
       <c r="A600" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B600" t="s" s="2">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="C600" t="s" s="2">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="D600" s="2"/>
       <c r="E600" t="s" s="2">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="F600" s="2"/>
       <c r="G600" t="s" s="2">
@@ -74028,16 +74036,16 @@
         <v>107</v>
       </c>
       <c r="L600" t="s" s="2">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="M600" t="s" s="2">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="N600" t="s" s="2">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="O600" t="s" s="2">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="P600" s="2"/>
       <c r="Q600" t="s" s="2">
@@ -74087,7 +74095,7 @@
         <v>22</v>
       </c>
       <c r="AG600" t="s" s="2">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="AH600" t="s" s="2">
         <v>76</v>
@@ -74104,17 +74112,17 @@
     </row>
     <row r="601">
       <c r="A601" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B601" t="s" s="2">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="C601" t="s" s="2">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="D601" s="2"/>
       <c r="E601" t="s" s="2">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="F601" s="2"/>
       <c r="G601" t="s" s="2">
@@ -74136,13 +74144,13 @@
         <v>236</v>
       </c>
       <c r="M601" t="s" s="2">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="N601" t="s" s="2">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="O601" t="s" s="2">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="P601" s="2"/>
       <c r="Q601" t="s" s="2">
@@ -74171,10 +74179,10 @@
         <v>579</v>
       </c>
       <c r="Z601" t="s" s="2">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="AA601" t="s" s="2">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="AB601" t="s" s="2">
         <v>22</v>
@@ -74192,7 +74200,7 @@
         <v>22</v>
       </c>
       <c r="AG601" t="s" s="2">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="AH601" t="s" s="2">
         <v>76</v>
@@ -74209,17 +74217,17 @@
     </row>
     <row r="602">
       <c r="A602" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B602" t="s" s="2">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="C602" t="s" s="2">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="D602" s="2"/>
       <c r="E602" t="s" s="2">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="F602" s="2"/>
       <c r="G602" t="s" s="2">
@@ -74238,16 +74246,16 @@
         <v>107</v>
       </c>
       <c r="L602" t="s" s="2">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="M602" t="s" s="2">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="N602" t="s" s="2">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="O602" t="s" s="2">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="P602" s="2"/>
       <c r="Q602" t="s" s="2">
@@ -74297,7 +74305,7 @@
         <v>22</v>
       </c>
       <c r="AG602" t="s" s="2">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="AH602" t="s" s="2">
         <v>76</v>
@@ -74314,13 +74322,13 @@
     </row>
     <row r="603">
       <c r="A603" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B603" t="s" s="2">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="C603" t="s" s="2">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="D603" s="2"/>
       <c r="E603" t="s" s="2">
@@ -74346,10 +74354,10 @@
         <v>769</v>
       </c>
       <c r="M603" t="s" s="2">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="N603" t="s" s="2">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="O603" s="2"/>
       <c r="P603" s="2"/>
@@ -74379,10 +74387,10 @@
         <v>579</v>
       </c>
       <c r="Z603" t="s" s="2">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="AA603" t="s" s="2">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="AB603" t="s" s="2">
         <v>22</v>
@@ -74400,7 +74408,7 @@
         <v>22</v>
       </c>
       <c r="AG603" t="s" s="2">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="AH603" t="s" s="2">
         <v>76</v>
@@ -74417,13 +74425,13 @@
     </row>
     <row r="604">
       <c r="A604" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B604" t="s" s="2">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C604" t="s" s="2">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="D604" s="2"/>
       <c r="E604" t="s" s="2">
@@ -74446,13 +74454,13 @@
         <v>107</v>
       </c>
       <c r="L604" t="s" s="2">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="M604" t="s" s="2">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="N604" t="s" s="2">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="O604" s="2"/>
       <c r="P604" s="2"/>
@@ -74503,7 +74511,7 @@
         <v>22</v>
       </c>
       <c r="AG604" t="s" s="2">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="AH604" t="s" s="2">
         <v>76</v>
@@ -74520,13 +74528,13 @@
     </row>
     <row r="605">
       <c r="A605" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B605" t="s" s="2">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="C605" t="s" s="2">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="D605" s="2"/>
       <c r="E605" t="s" s="2">
@@ -74552,13 +74560,13 @@
         <v>236</v>
       </c>
       <c r="M605" t="s" s="2">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="N605" t="s" s="2">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="O605" t="s" s="2">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="P605" s="2"/>
       <c r="Q605" t="s" s="2">
@@ -74588,7 +74596,7 @@
       </c>
       <c r="Z605" s="2"/>
       <c r="AA605" t="s" s="2">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="AB605" t="s" s="2">
         <v>22</v>
@@ -74606,7 +74614,7 @@
         <v>22</v>
       </c>
       <c r="AG605" t="s" s="2">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="AH605" t="s" s="2">
         <v>76</v>
@@ -74623,13 +74631,13 @@
     </row>
     <row r="606">
       <c r="A606" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B606" t="s" s="2">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="C606" t="s" s="2">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="D606" s="2"/>
       <c r="E606" t="s" s="2">
@@ -74652,16 +74660,16 @@
         <v>107</v>
       </c>
       <c r="L606" t="s" s="2">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="M606" t="s" s="2">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="N606" t="s" s="2">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="O606" t="s" s="2">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="P606" s="2"/>
       <c r="Q606" t="s" s="2">
@@ -74711,7 +74719,7 @@
         <v>22</v>
       </c>
       <c r="AG606" t="s" s="2">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="AH606" t="s" s="2">
         <v>76</v>
@@ -74728,13 +74736,13 @@
     </row>
     <row r="607">
       <c r="A607" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B607" t="s" s="2">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="C607" t="s" s="2">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="D607" s="2"/>
       <c r="E607" t="s" s="2">
@@ -74757,13 +74765,13 @@
         <v>22</v>
       </c>
       <c r="L607" t="s" s="2">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="M607" t="s" s="2">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="N607" t="s" s="2">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="O607" s="2"/>
       <c r="P607" s="2"/>
@@ -74814,7 +74822,7 @@
         <v>22</v>
       </c>
       <c r="AG607" t="s" s="2">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="AH607" t="s" s="2">
         <v>76</v>
@@ -74831,17 +74839,17 @@
     </row>
     <row r="608">
       <c r="A608" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B608" t="s" s="2">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="C608" t="s" s="2">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="D608" s="2"/>
       <c r="E608" t="s" s="2">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="F608" s="2"/>
       <c r="G608" t="s" s="2">
@@ -74863,13 +74871,13 @@
         <v>730</v>
       </c>
       <c r="M608" t="s" s="2">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="N608" t="s" s="2">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="O608" t="s" s="2">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="P608" s="2"/>
       <c r="Q608" t="s" s="2">
@@ -74919,7 +74927,7 @@
         <v>22</v>
       </c>
       <c r="AG608" t="s" s="2">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="AH608" t="s" s="2">
         <v>76</v>
@@ -74936,13 +74944,13 @@
     </row>
     <row r="609">
       <c r="A609" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B609" t="s" s="2">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="C609" t="s" s="2">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="D609" s="2"/>
       <c r="E609" t="s" s="2">
@@ -74965,16 +74973,16 @@
         <v>107</v>
       </c>
       <c r="L609" t="s" s="2">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="M609" t="s" s="2">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="N609" t="s" s="2">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="O609" t="s" s="2">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="P609" s="2"/>
       <c r="Q609" t="s" s="2">
@@ -75024,7 +75032,7 @@
         <v>22</v>
       </c>
       <c r="AG609" t="s" s="2">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="AH609" t="s" s="2">
         <v>76</v>
@@ -75041,17 +75049,17 @@
     </row>
     <row r="610">
       <c r="A610" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B610" t="s" s="2">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="C610" t="s" s="2">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="D610" s="2"/>
       <c r="E610" t="s" s="2">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="F610" s="2"/>
       <c r="G610" t="s" s="2">
@@ -75073,16 +75081,16 @@
         <v>236</v>
       </c>
       <c r="M610" t="s" s="2">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="N610" t="s" s="2">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="O610" t="s" s="2">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="P610" t="s" s="2">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="Q610" t="s" s="2">
         <v>22</v>
@@ -75131,7 +75139,7 @@
         <v>22</v>
       </c>
       <c r="AG610" t="s" s="2">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="AH610" t="s" s="2">
         <v>76</v>
@@ -75148,13 +75156,13 @@
     </row>
     <row r="611">
       <c r="A611" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B611" t="s" s="2">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="C611" t="s" s="2">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="D611" s="2"/>
       <c r="E611" t="s" s="2">
@@ -75177,13 +75185,13 @@
         <v>22</v>
       </c>
       <c r="L611" t="s" s="2">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="M611" t="s" s="2">
         <v>53</v>
       </c>
       <c r="N611" t="s" s="2">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="O611" s="2"/>
       <c r="P611" s="2"/>
@@ -75234,7 +75242,7 @@
         <v>22</v>
       </c>
       <c r="AG611" t="s" s="2">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="AH611" t="s" s="2">
         <v>76</v>
@@ -75251,13 +75259,13 @@
     </row>
     <row r="612">
       <c r="A612" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B612" t="s" s="2">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C612" t="s" s="2">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="D612" s="2"/>
       <c r="E612" t="s" s="2">
@@ -75283,10 +75291,10 @@
         <v>86</v>
       </c>
       <c r="M612" t="s" s="2">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="N612" t="s" s="2">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="O612" s="2"/>
       <c r="P612" s="2"/>
@@ -75337,7 +75345,7 @@
         <v>22</v>
       </c>
       <c r="AG612" t="s" s="2">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="AH612" t="s" s="2">
         <v>76</v>
@@ -75354,13 +75362,13 @@
     </row>
     <row r="613">
       <c r="A613" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B613" t="s" s="2">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="C613" t="s" s="2">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="D613" s="2"/>
       <c r="E613" t="s" s="2">
@@ -75383,16 +75391,16 @@
         <v>22</v>
       </c>
       <c r="L613" t="s" s="2">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="M613" t="s" s="2">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="N613" t="s" s="2">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="O613" t="s" s="2">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="P613" s="2"/>
       <c r="Q613" t="s" s="2">
@@ -75442,7 +75450,7 @@
         <v>22</v>
       </c>
       <c r="AG613" t="s" s="2">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="AH613" t="s" s="2">
         <v>76</v>
@@ -75459,13 +75467,13 @@
     </row>
     <row r="614">
       <c r="A614" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B614" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C614" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D614" s="2"/>
       <c r="E614" t="s" s="2">
@@ -75491,10 +75499,10 @@
         <v>78</v>
       </c>
       <c r="M614" t="s" s="2">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="N614" t="s" s="2">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="O614" t="s" s="2">
         <v>405</v>
@@ -75547,7 +75555,7 @@
         <v>22</v>
       </c>
       <c r="AG614" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="AH614" t="s" s="2">
         <v>76</v>
@@ -75559,18 +75567,18 @@
         <v>82</v>
       </c>
       <c r="AK614" t="s" s="2">
-        <v>1400</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B615" t="s" s="2">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C615" t="s" s="2">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D615" s="2"/>
       <c r="E615" t="s" s="2">
@@ -75667,13 +75675,13 @@
     </row>
     <row r="616">
       <c r="A616" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B616" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C616" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D616" s="2"/>
       <c r="E616" t="s" s="2">
@@ -75772,13 +75780,13 @@
     </row>
     <row r="617">
       <c r="A617" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B617" t="s" s="2">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C617" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D617" t="s" s="2">
         <v>410</v>
@@ -75806,10 +75814,10 @@
         <v>411</v>
       </c>
       <c r="M617" t="s" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="N617" t="s" s="2">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="O617" s="2"/>
       <c r="P617" s="2"/>
@@ -75877,7 +75885,7 @@
     </row>
     <row r="618">
       <c r="A618" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B618" t="s" s="2">
         <v>420</v>
@@ -75912,7 +75920,7 @@
         <v>416</v>
       </c>
       <c r="N618" t="s" s="2">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="O618" t="s" s="2">
         <v>418</v>
@@ -75984,13 +75992,13 @@
     </row>
     <row r="619">
       <c r="A619" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B619" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C619" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D619" s="2"/>
       <c r="E619" t="s" s="2">
@@ -76087,13 +76095,13 @@
     </row>
     <row r="620">
       <c r="A620" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B620" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C620" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D620" s="2"/>
       <c r="E620" t="s" s="2">
@@ -76188,13 +76196,13 @@
     </row>
     <row r="621">
       <c r="A621" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B621" t="s" s="2">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C621" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D621" t="s" s="2">
         <v>388</v>
@@ -76295,13 +76303,13 @@
     </row>
     <row r="622">
       <c r="A622" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B622" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="C622" t="s" s="2">
         <v>1007</v>
-      </c>
-      <c r="C622" t="s" s="2">
-        <v>1005</v>
       </c>
       <c r="D622" t="s" s="2">
         <v>425</v>
@@ -76329,10 +76337,10 @@
         <v>426</v>
       </c>
       <c r="M622" t="s" s="2">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="N622" t="s" s="2">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="O622" s="2"/>
       <c r="P622" s="2"/>
@@ -76400,13 +76408,13 @@
     </row>
     <row r="623">
       <c r="A623" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B623" t="s" s="2">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C623" t="s" s="2">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D623" s="2"/>
       <c r="E623" t="s" s="2">
@@ -76503,7 +76511,7 @@
     </row>
     <row r="624">
       <c r="A624" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B624" t="s" s="2">
         <v>437</v>
@@ -76538,7 +76546,7 @@
         <v>431</v>
       </c>
       <c r="N624" t="s" s="2">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="O624" s="2"/>
       <c r="P624" t="s" s="2">
@@ -76610,7 +76618,7 @@
     </row>
     <row r="625">
       <c r="A625" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B625" t="s" s="2">
         <v>442</v>
@@ -76715,7 +76723,7 @@
     </row>
     <row r="626">
       <c r="A626" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B626" t="s" s="2">
         <v>447</v>
@@ -76820,7 +76828,7 @@
     </row>
     <row r="627">
       <c r="A627" t="s" s="2">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B627" t="s" s="2">
         <v>454</v>
@@ -76927,13 +76935,13 @@
     </row>
     <row r="628">
       <c r="A628" t="s" s="2">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B628" t="s" s="2">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="C628" t="s" s="2">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="D628" s="2"/>
       <c r="E628" t="s" s="2">
@@ -76959,10 +76967,10 @@
         <v>78</v>
       </c>
       <c r="M628" t="s" s="2">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="N628" t="s" s="2">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="O628" s="2"/>
       <c r="P628" s="2"/>
@@ -77013,7 +77021,7 @@
         <v>22</v>
       </c>
       <c r="AG628" t="s" s="2">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="AH628" t="s" s="2">
         <v>76</v>
@@ -77030,13 +77038,13 @@
     </row>
     <row r="629">
       <c r="A629" t="s" s="2">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B629" t="s" s="2">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="C629" t="s" s="2">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="D629" s="2"/>
       <c r="E629" t="s" s="2">
@@ -77133,13 +77141,13 @@
     </row>
     <row r="630">
       <c r="A630" t="s" s="2">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B630" t="s" s="2">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="C630" t="s" s="2">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="D630" s="2"/>
       <c r="E630" t="s" s="2">
@@ -77234,13 +77242,13 @@
     </row>
     <row r="631">
       <c r="A631" t="s" s="2">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B631" t="s" s="2">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="C631" t="s" s="2">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="D631" t="s" s="2">
         <v>343</v>
@@ -77265,13 +77273,13 @@
         <v>22</v>
       </c>
       <c r="L631" t="s" s="2">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="M631" t="s" s="2">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="N631" t="s" s="2">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="O631" s="2"/>
       <c r="P631" s="2"/>
@@ -77339,13 +77347,13 @@
     </row>
     <row r="632">
       <c r="A632" t="s" s="2">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B632" t="s" s="2">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="C632" t="s" s="2">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="D632" t="s" s="2">
         <v>348</v>
@@ -77370,13 +77378,13 @@
         <v>22</v>
       </c>
       <c r="L632" t="s" s="2">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="M632" t="s" s="2">
         <v>350</v>
       </c>
       <c r="N632" t="s" s="2">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="O632" s="2"/>
       <c r="P632" s="2"/>
@@ -77444,13 +77452,13 @@
     </row>
     <row r="633">
       <c r="A633" t="s" s="2">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B633" t="s" s="2">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="C633" t="s" s="2">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="D633" s="2"/>
       <c r="E633" t="s" s="2">
@@ -77473,10 +77481,10 @@
         <v>22</v>
       </c>
       <c r="L633" t="s" s="2">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="M633" t="s" s="2">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="N633" t="s" s="2">
         <v>355</v>
@@ -77530,7 +77538,7 @@
         <v>22</v>
       </c>
       <c r="AG633" t="s" s="2">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="AH633" t="s" s="2">
         <v>76</v>
@@ -77547,7 +77555,7 @@
     </row>
     <row r="634">
       <c r="A634" t="s" s="2">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B634" t="s" s="2">
         <v>130</v>
@@ -77579,10 +77587,10 @@
         <v>78</v>
       </c>
       <c r="M634" t="s" s="2">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="N634" t="s" s="2">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="O634" s="2"/>
       <c r="P634" s="2"/>
@@ -77650,7 +77658,7 @@
     </row>
     <row r="635">
       <c r="A635" t="s" s="2">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B635" t="s" s="2">
         <v>134</v>
@@ -77753,7 +77761,7 @@
     </row>
     <row r="636">
       <c r="A636" t="s" s="2">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B636" t="s" s="2">
         <v>135</v>
@@ -77856,7 +77864,7 @@
     </row>
     <row r="637">
       <c r="A637" t="s" s="2">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B637" t="s" s="2">
         <v>137</v>
@@ -77902,7 +77910,7 @@
       </c>
       <c r="R637" s="2"/>
       <c r="S637" t="s" s="2">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="T637" t="s" s="2">
         <v>22</v>
@@ -77961,7 +77969,7 @@
     </row>
     <row r="638">
       <c r="A638" t="s" s="2">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B638" t="s" s="2">
         <v>142</v>
@@ -77993,10 +78001,10 @@
         <v>172</v>
       </c>
       <c r="M638" t="s" s="2">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="N638" t="s" s="2">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="O638" s="2"/>
       <c r="P638" s="2"/>
@@ -78062,7 +78070,7 @@
     </row>
     <row r="639">
       <c r="A639" t="s" s="2">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B639" t="s" s="2">
         <v>130</v>
@@ -78094,10 +78102,10 @@
         <v>78</v>
       </c>
       <c r="M639" t="s" s="2">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="N639" t="s" s="2">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="O639" s="2"/>
       <c r="P639" s="2"/>
@@ -78165,7 +78173,7 @@
     </row>
     <row r="640">
       <c r="A640" t="s" s="2">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B640" t="s" s="2">
         <v>134</v>
@@ -78268,7 +78276,7 @@
     </row>
     <row r="641">
       <c r="A641" t="s" s="2">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B641" t="s" s="2">
         <v>135</v>
@@ -78371,7 +78379,7 @@
     </row>
     <row r="642">
       <c r="A642" t="s" s="2">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B642" t="s" s="2">
         <v>137</v>
@@ -78417,7 +78425,7 @@
       </c>
       <c r="R642" s="2"/>
       <c r="S642" t="s" s="2">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="T642" t="s" s="2">
         <v>22</v>
@@ -78476,7 +78484,7 @@
     </row>
     <row r="643">
       <c r="A643" t="s" s="2">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B643" t="s" s="2">
         <v>142</v>
@@ -78508,10 +78516,10 @@
         <v>172</v>
       </c>
       <c r="M643" t="s" s="2">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="N643" t="s" s="2">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="O643" s="2"/>
       <c r="P643" s="2"/>
@@ -78577,13 +78585,13 @@
     </row>
     <row r="644">
       <c r="A644" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B644" t="s" s="2">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="C644" t="s" s="2">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="D644" s="2"/>
       <c r="E644" t="s" s="2">
@@ -78609,13 +78617,13 @@
         <v>78</v>
       </c>
       <c r="M644" t="s" s="2">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="N644" t="s" s="2">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="O644" t="s" s="2">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="P644" s="2"/>
       <c r="Q644" t="s" s="2">
@@ -78665,7 +78673,7 @@
         <v>22</v>
       </c>
       <c r="AG644" t="s" s="2">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="AH644" t="s" s="2">
         <v>76</v>
@@ -78682,13 +78690,13 @@
     </row>
     <row r="645">
       <c r="A645" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B645" t="s" s="2">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="C645" t="s" s="2">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="D645" s="2"/>
       <c r="E645" t="s" s="2">
@@ -78785,13 +78793,13 @@
     </row>
     <row r="646">
       <c r="A646" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B646" t="s" s="2">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="C646" t="s" s="2">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="D646" s="2"/>
       <c r="E646" t="s" s="2">
@@ -78890,13 +78898,13 @@
     </row>
     <row r="647">
       <c r="A647" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B647" t="s" s="2">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="C647" t="s" s="2">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="D647" s="2"/>
       <c r="E647" t="s" s="2">
@@ -78997,13 +79005,13 @@
     </row>
     <row r="648">
       <c r="A648" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B648" t="s" s="2">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="C648" t="s" s="2">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="D648" s="2"/>
       <c r="E648" t="s" s="2">
@@ -79029,14 +79037,14 @@
         <v>117</v>
       </c>
       <c r="M648" t="s" s="2">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="N648" t="s" s="2">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="O648" s="2"/>
       <c r="P648" t="s" s="2">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="Q648" t="s" s="2">
         <v>22</v>
@@ -79085,7 +79093,7 @@
         <v>22</v>
       </c>
       <c r="AG648" t="s" s="2">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="AH648" t="s" s="2">
         <v>76</v>
@@ -79102,13 +79110,13 @@
     </row>
     <row r="649">
       <c r="A649" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B649" t="s" s="2">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="C649" t="s" s="2">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="D649" s="2"/>
       <c r="E649" t="s" s="2">
@@ -79131,17 +79139,17 @@
         <v>107</v>
       </c>
       <c r="L649" t="s" s="2">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="M649" t="s" s="2">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="N649" t="s" s="2">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="O649" s="2"/>
       <c r="P649" t="s" s="2">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="Q649" t="s" s="2">
         <v>22</v>
@@ -79190,7 +79198,7 @@
         <v>22</v>
       </c>
       <c r="AG649" t="s" s="2">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="AH649" t="s" s="2">
         <v>76</v>
@@ -79202,18 +79210,18 @@
         <v>22</v>
       </c>
       <c r="AK649" t="s" s="2">
-        <v>1466</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B650" t="s" s="2">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="C650" t="s" s="2">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="D650" s="2"/>
       <c r="E650" t="s" s="2">
@@ -79310,13 +79318,13 @@
     </row>
     <row r="651">
       <c r="A651" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B651" t="s" s="2">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="C651" t="s" s="2">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="D651" s="2"/>
       <c r="E651" t="s" s="2">
@@ -79415,13 +79423,13 @@
     </row>
     <row r="652">
       <c r="A652" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B652" t="s" s="2">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="C652" t="s" s="2">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="D652" s="2"/>
       <c r="E652" t="s" s="2">
@@ -79444,13 +79452,13 @@
         <v>107</v>
       </c>
       <c r="L652" t="s" s="2">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="M652" t="s" s="2">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="N652" t="s" s="2">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="O652" s="2"/>
       <c r="P652" s="2"/>
@@ -79501,7 +79509,7 @@
         <v>22</v>
       </c>
       <c r="AG652" t="s" s="2">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="AH652" t="s" s="2">
         <v>76</v>
@@ -79518,13 +79526,13 @@
     </row>
     <row r="653">
       <c r="A653" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B653" t="s" s="2">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="C653" t="s" s="2">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="D653" s="2"/>
       <c r="E653" t="s" s="2">
@@ -79547,19 +79555,19 @@
         <v>107</v>
       </c>
       <c r="L653" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="M653" t="s" s="2">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="N653" t="s" s="2">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="O653" t="s" s="2">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="P653" t="s" s="2">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="Q653" t="s" s="2">
         <v>22</v>
@@ -79608,7 +79616,7 @@
         <v>22</v>
       </c>
       <c r="AG653" t="s" s="2">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="AH653" t="s" s="2">
         <v>76</v>
@@ -79625,13 +79633,13 @@
     </row>
     <row r="654">
       <c r="A654" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B654" t="s" s="2">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="C654" t="s" s="2">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="D654" s="2"/>
       <c r="E654" t="s" s="2">
@@ -79654,13 +79662,13 @@
         <v>107</v>
       </c>
       <c r="L654" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="M654" t="s" s="2">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="N654" t="s" s="2">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="O654" s="2"/>
       <c r="P654" s="2"/>
@@ -79711,7 +79719,7 @@
         <v>22</v>
       </c>
       <c r="AG654" t="s" s="2">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="AH654" t="s" s="2">
         <v>76</v>
@@ -79728,13 +79736,13 @@
     </row>
     <row r="655">
       <c r="A655" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B655" t="s" s="2">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C655" t="s" s="2">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="D655" s="2"/>
       <c r="E655" t="s" s="2">
@@ -79760,16 +79768,16 @@
         <v>415</v>
       </c>
       <c r="M655" t="s" s="2">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="N655" t="s" s="2">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="O655" t="s" s="2">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="P655" t="s" s="2">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="Q655" t="s" s="2">
         <v>22</v>
@@ -79818,7 +79826,7 @@
         <v>22</v>
       </c>
       <c r="AG655" t="s" s="2">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="AH655" t="s" s="2">
         <v>76</v>
@@ -79835,13 +79843,13 @@
     </row>
     <row r="656">
       <c r="A656" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B656" t="s" s="2">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C656" t="s" s="2">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="D656" s="2"/>
       <c r="E656" t="s" s="2">
@@ -79867,16 +79875,16 @@
         <v>415</v>
       </c>
       <c r="M656" t="s" s="2">
+        <v>1489</v>
+      </c>
+      <c r="N656" t="s" s="2">
+        <v>1490</v>
+      </c>
+      <c r="O656" t="s" s="2">
+        <v>1486</v>
+      </c>
+      <c r="P656" t="s" s="2">
         <v>1487</v>
-      </c>
-      <c r="N656" t="s" s="2">
-        <v>1488</v>
-      </c>
-      <c r="O656" t="s" s="2">
-        <v>1484</v>
-      </c>
-      <c r="P656" t="s" s="2">
-        <v>1485</v>
       </c>
       <c r="Q656" t="s" s="2">
         <v>22</v>
@@ -79925,7 +79933,7 @@
         <v>22</v>
       </c>
       <c r="AG656" t="s" s="2">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="AH656" t="s" s="2">
         <v>76</v>
@@ -79942,13 +79950,13 @@
     </row>
     <row r="657">
       <c r="A657" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B657" t="s" s="2">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="C657" t="s" s="2">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="D657" s="2"/>
       <c r="E657" t="s" s="2">
@@ -79974,10 +79982,10 @@
         <v>172</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="N657" t="s" s="2">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="O657" s="2"/>
       <c r="P657" s="2"/>
@@ -80007,10 +80015,10 @@
         <v>177</v>
       </c>
       <c r="Z657" t="s" s="2">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="AA657" t="s" s="2">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="AB657" t="s" s="2">
         <v>22</v>
@@ -80028,7 +80036,7 @@
         <v>22</v>
       </c>
       <c r="AG657" t="s" s="2">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="AH657" t="s" s="2">
         <v>76</v>
@@ -80045,13 +80053,13 @@
     </row>
     <row r="658">
       <c r="A658" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B658" t="s" s="2">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="C658" t="s" s="2">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="D658" s="2"/>
       <c r="E658" t="s" s="2">
@@ -80074,13 +80082,13 @@
         <v>107</v>
       </c>
       <c r="L658" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="N658" t="s" s="2">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="O658" s="2"/>
       <c r="P658" s="2"/>
@@ -80088,7 +80096,7 @@
         <v>22</v>
       </c>
       <c r="R658" t="s" s="2">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="S658" t="s" s="2">
         <v>22</v>
@@ -80133,7 +80141,7 @@
         <v>22</v>
       </c>
       <c r="AG658" t="s" s="2">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="AH658" t="s" s="2">
         <v>76</v>
@@ -80150,13 +80158,13 @@
     </row>
     <row r="659">
       <c r="A659" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B659" t="s" s="2">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="C659" t="s" s="2">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="D659" s="2"/>
       <c r="E659" t="s" s="2">
@@ -80179,13 +80187,13 @@
         <v>107</v>
       </c>
       <c r="L659" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="M659" t="s" s="2">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="N659" t="s" s="2">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="O659" s="2"/>
       <c r="P659" s="2"/>
@@ -80236,7 +80244,7 @@
         <v>22</v>
       </c>
       <c r="AG659" t="s" s="2">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="AH659" t="s" s="2">
         <v>76</v>
@@ -80253,13 +80261,13 @@
     </row>
     <row r="660">
       <c r="A660" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B660" t="s" s="2">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="C660" t="s" s="2">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="D660" s="2"/>
       <c r="E660" t="s" s="2">
@@ -80285,10 +80293,10 @@
         <v>415</v>
       </c>
       <c r="M660" t="s" s="2">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="N660" t="s" s="2">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="O660" s="2"/>
       <c r="P660" s="2"/>
@@ -80339,7 +80347,7 @@
         <v>22</v>
       </c>
       <c r="AG660" t="s" s="2">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="AH660" t="s" s="2">
         <v>76</v>
@@ -80356,13 +80364,13 @@
     </row>
     <row r="661">
       <c r="A661" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B661" t="s" s="2">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="C661" t="s" s="2">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D661" s="2"/>
       <c r="E661" t="s" s="2">
@@ -80388,10 +80396,10 @@
         <v>415</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="N661" t="s" s="2">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="O661" s="2"/>
       <c r="P661" s="2"/>
@@ -80442,7 +80450,7 @@
         <v>22</v>
       </c>
       <c r="AG661" t="s" s="2">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="AH661" t="s" s="2">
         <v>76</v>
@@ -80459,13 +80467,13 @@
     </row>
     <row r="662">
       <c r="A662" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B662" t="s" s="2">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="C662" t="s" s="2">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="D662" s="2"/>
       <c r="E662" t="s" s="2">
@@ -80491,10 +80499,10 @@
         <v>172</v>
       </c>
       <c r="M662" t="s" s="2">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="N662" t="s" s="2">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="O662" s="2"/>
       <c r="P662" s="2"/>
@@ -80524,10 +80532,10 @@
         <v>177</v>
       </c>
       <c r="Z662" t="s" s="2">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="AA662" t="s" s="2">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="AB662" t="s" s="2">
         <v>22</v>
@@ -80545,7 +80553,7 @@
         <v>22</v>
       </c>
       <c r="AG662" t="s" s="2">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="AH662" t="s" s="2">
         <v>76</v>
@@ -80562,13 +80570,13 @@
     </row>
     <row r="663">
       <c r="A663" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B663" t="s" s="2">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="C663" t="s" s="2">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="D663" s="2"/>
       <c r="E663" t="s" s="2">
@@ -80594,13 +80602,13 @@
         <v>172</v>
       </c>
       <c r="M663" t="s" s="2">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="N663" t="s" s="2">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="O663" t="s" s="2">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="P663" s="2"/>
       <c r="Q663" t="s" s="2">
@@ -80630,7 +80638,7 @@
       </c>
       <c r="Z663" s="2"/>
       <c r="AA663" t="s" s="2">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="AB663" t="s" s="2">
         <v>22</v>
@@ -80648,7 +80656,7 @@
         <v>22</v>
       </c>
       <c r="AG663" t="s" s="2">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="AH663" t="s" s="2">
         <v>76</v>
@@ -80665,13 +80673,13 @@
     </row>
     <row r="664">
       <c r="A664" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B664" t="s" s="2">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="C664" t="s" s="2">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="D664" s="2"/>
       <c r="E664" t="s" s="2">
@@ -80694,16 +80702,16 @@
         <v>107</v>
       </c>
       <c r="L664" t="s" s="2">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="M664" t="s" s="2">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="N664" t="s" s="2">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="O664" t="s" s="2">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="P664" s="2"/>
       <c r="Q664" t="s" s="2">
@@ -80753,7 +80761,7 @@
         <v>22</v>
       </c>
       <c r="AG664" t="s" s="2">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="AH664" t="s" s="2">
         <v>76</v>
@@ -80770,13 +80778,13 @@
     </row>
     <row r="665">
       <c r="A665" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B665" t="s" s="2">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="C665" t="s" s="2">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="D665" s="2"/>
       <c r="E665" t="s" s="2">
@@ -80802,16 +80810,16 @@
         <v>172</v>
       </c>
       <c r="M665" t="s" s="2">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="N665" t="s" s="2">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="O665" t="s" s="2">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="P665" t="s" s="2">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="Q665" t="s" s="2">
         <v>22</v>
@@ -80839,10 +80847,10 @@
         <v>177</v>
       </c>
       <c r="Z665" t="s" s="2">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="AA665" t="s" s="2">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="AB665" t="s" s="2">
         <v>22</v>
@@ -80860,7 +80868,7 @@
         <v>22</v>
       </c>
       <c r="AG665" t="s" s="2">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="AH665" t="s" s="2">
         <v>76</v>
@@ -80877,13 +80885,13 @@
     </row>
     <row r="666">
       <c r="A666" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B666" t="s" s="2">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="C666" t="s" s="2">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="D666" s="2"/>
       <c r="E666" t="s" s="2">
@@ -80909,10 +80917,10 @@
         <v>202</v>
       </c>
       <c r="M666" t="s" s="2">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="N666" t="s" s="2">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="O666" s="2"/>
       <c r="P666" s="2"/>
@@ -80963,7 +80971,7 @@
         <v>22</v>
       </c>
       <c r="AG666" t="s" s="2">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="AH666" t="s" s="2">
         <v>76</v>
@@ -80980,13 +80988,13 @@
     </row>
     <row r="667">
       <c r="A667" t="s" s="2">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B667" t="s" s="2">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C667" t="s" s="2">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D667" s="2"/>
       <c r="E667" t="s" s="2">
@@ -81012,13 +81020,13 @@
         <v>236</v>
       </c>
       <c r="M667" t="s" s="2">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="N667" t="s" s="2">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="O667" t="s" s="2">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="P667" s="2"/>
       <c r="Q667" t="s" s="2">
@@ -81047,10 +81055,10 @@
         <v>185</v>
       </c>
       <c r="Z667" t="s" s="2">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="AA667" t="s" s="2">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="AB667" t="s" s="2">
         <v>22</v>
@@ -81068,7 +81076,7 @@
         <v>22</v>
       </c>
       <c r="AG667" t="s" s="2">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="AH667" t="s" s="2">
         <v>76</v>
@@ -81085,7 +81093,7 @@
     </row>
     <row r="668">
       <c r="A668" t="s" s="2">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B668" t="s" s="2">
         <v>130</v>
@@ -81117,10 +81125,10 @@
         <v>78</v>
       </c>
       <c r="M668" t="s" s="2">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="N668" t="s" s="2">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="O668" s="2"/>
       <c r="P668" s="2"/>
@@ -81188,7 +81196,7 @@
     </row>
     <row r="669">
       <c r="A669" t="s" s="2">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B669" t="s" s="2">
         <v>134</v>
@@ -81291,7 +81299,7 @@
     </row>
     <row r="670">
       <c r="A670" t="s" s="2">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B670" t="s" s="2">
         <v>135</v>
@@ -81394,7 +81402,7 @@
     </row>
     <row r="671">
       <c r="A671" t="s" s="2">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B671" t="s" s="2">
         <v>137</v>
@@ -81440,7 +81448,7 @@
       </c>
       <c r="R671" s="2"/>
       <c r="S671" t="s" s="2">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="T671" t="s" s="2">
         <v>22</v>
@@ -81499,7 +81507,7 @@
     </row>
     <row r="672">
       <c r="A672" t="s" s="2">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B672" t="s" s="2">
         <v>142</v>
@@ -81531,10 +81539,10 @@
         <v>143</v>
       </c>
       <c r="M672" t="s" s="2">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="N672" t="s" s="2">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="O672" s="2"/>
       <c r="P672" s="2"/>
